--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000182</v>
+        <v>115000184</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.07.28</t>
+          <t>115.07.30</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>05  08  13  23  31</t>
+          <t>04  07  08  16  38</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000181</v>
+        <v>115000183</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.07.27</t>
+          <t>115.07.29</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>07  16  19  24  32</t>
+          <t>05  14  32  33  36</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000180</v>
+        <v>115000182</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.07.25</t>
+          <t>115.07.28</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>08  12  16  23  39</t>
+          <t>05  08  13  23  31</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000179</v>
+        <v>115000181</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.07.24</t>
+          <t>115.07.27</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>05  17  27  29  36</t>
+          <t>07  16  19  24  32</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000178</v>
+        <v>115000180</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.07.23</t>
+          <t>115.07.25</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>12  14  19  25  26</t>
+          <t>08  12  16  23  39</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000177</v>
+        <v>115000179</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.07.22</t>
+          <t>115.07.24</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>03  14  19  21  31</t>
+          <t>05  17  27  29  36</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000176</v>
+        <v>115000178</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.07.21</t>
+          <t>115.07.23</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>12  19  27  37  39</t>
+          <t>12  14  19  25  26</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000175</v>
+        <v>115000177</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.07.20</t>
+          <t>115.07.22</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>10  12  13  20  24</t>
+          <t>03  14  19  21  31</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000174</v>
+        <v>115000176</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.07.18</t>
+          <t>115.07.21</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>18  29  33  34  37</t>
+          <t>12  19  27  37  39</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000173</v>
+        <v>115000175</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.07.17</t>
+          <t>115.07.20</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>10  12  28  29  35</t>
+          <t>10  12  13  20  24</t>
         </is>
       </c>
     </row>
@@ -1354,16 +1354,16 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.07.27</t>
+          <t>115.07.30</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>19  22  28  31  33  35</t>
+          <t>08  14  17  19  21  23</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
@@ -1374,16 +1374,16 @@
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.07.23</t>
+          <t>115.07.27</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>08  10  13  21  29  31</t>
+          <t>19  22  28  31  33  35</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -1394,76 +1394,76 @@
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.07.20</t>
+          <t>115.07.23</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>06  12  13  23  29  31</t>
+          <t>08  10  13  21  29  31</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.07.16</t>
+          <t>115.07.20</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>17  23  25  29  34  36</t>
+          <t>06  12  13  23  29  31</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.07.13</t>
+          <t>115.07.16</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>11  24  29  32  35  38</t>
+          <t>17  23  25  29  34  36</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000055</v>
+        <v>115000056</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.07.09</t>
+          <t>115.07.13</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>10  22  24  29  35  37</t>
+          <t>11  24  29  32  35  38</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -1474,49 +1474,63 @@
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000054</v>
+        <v>115000055</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.07.06</t>
+          <t>115.07.09</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>04  12  15  24  30  31</t>
+          <t>10  22  24  29  35  37</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
+        <v>115000054</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>115.07.06</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>04  12  15  24  30  31</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1" s="5">
+      <c r="A10" s="4" t="n">
         <v>115000053</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>115.07.02</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>02  11  13  21  22  35</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>03</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="20" customHeight="1" s="5">
-      <c r="A10" s="4" t="n"/>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n"/>
@@ -2158,120 +2172,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>07/28(二)</t>
+          <t>07/29(三)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>7  1  6</t>
+          <t>8  4  6</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>07/27(一)</t>
+          <t>07/28(二)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>6  0  2</t>
+          <t>7  1  6</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>07/25(六)</t>
+          <t>07/27(一)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>1  8  3</t>
+          <t>6  0  2</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>07/24(五)</t>
+          <t>07/25(六)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>5  4  0</t>
+          <t>1  8  3</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>07/23(四)</t>
+          <t>07/24(五)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>0  1  8</t>
+          <t>5  4  0</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>07/22(三)</t>
+          <t>07/23(四)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>5  0  2</t>
+          <t>0  1  8</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>07/21(二)</t>
+          <t>07/22(三)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>4  1  8</t>
+          <t>5  0  2</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>07/20(一)</t>
+          <t>07/21(二)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>3  0  1</t>
+          <t>4  1  8</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>07/18(六)</t>
+          <t>07/20(一)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>6  6  7</t>
+          <t>3  0  1</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>07/17(五)</t>
+          <t>07/18(六)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>4  1  3</t>
+          <t>6  6  7</t>
         </is>
       </c>
     </row>
@@ -2504,84 +2518,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>07/27(一)</t>
+          <t>07/29(三)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>5  9  1  0</t>
+          <t>7  6  8  5</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>07/25(六)</t>
+          <t>07/28(二)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>9  0  4  8</t>
+          <t>0  4  3  3</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>07/24(五)</t>
+          <t>07/27(一)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>3  1  0  8</t>
+          <t>5  9  1  0</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>07/23(四)</t>
+          <t>07/25(六)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>5  3  5  1</t>
+          <t>9  0  4  8</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>07/22(三)</t>
+          <t>07/24(五)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>7  9  4  7</t>
+          <t>3  1  0  8</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>07/21(二)</t>
+          <t>07/23(四)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>0  7  5  7</t>
+          <t>5  3  5  1</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>07/20(一)</t>
+          <t>07/22(三)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>4  0  1  4</t>
+          <t>7  9  4  7</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2589,36 +2603,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>07/18(六)</t>
+          <t>07/21(二)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>7  9  9  5</t>
+          <t>0  7  5  7</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>07/17(五)</t>
+          <t>07/20(一)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>7  4  2  0</t>
+          <t>4  0  1  4</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>07/16(四)</t>
+          <t>07/18(六)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>6  4  2  7</t>
+          <t>7  9  9  5</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000182</v>
+        <v>115000177</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.07.28</t>
+          <t>115.07.22</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>05  08  13  23  31</t>
+          <t>03  14  19  21  31</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000181</v>
+        <v>115000178</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.07.27</t>
+          <t>115.07.23</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>07  16  19  24  32</t>
+          <t>12  14  19  25  26</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000180</v>
+        <v>115000179</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.07.25</t>
+          <t>115.07.24</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>08  12  16  23  39</t>
+          <t>05  17  27  29  36</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000179</v>
+        <v>115000180</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.07.24</t>
+          <t>115.07.25</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>05  17  27  29  36</t>
+          <t>08  12  16  23  39</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000178</v>
+        <v>115000181</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.07.23</t>
+          <t>115.07.27</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>12  14  19  25  26</t>
+          <t>07  16  19  24  32</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000177</v>
+        <v>115000182</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.07.22</t>
+          <t>115.07.28</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>03  14  19  21  31</t>
+          <t>05  08  13  23  31</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000176</v>
+        <v>115000183</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.07.21</t>
+          <t>115.07.29</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>12  19  27  37  39</t>
+          <t>05  14  32  33  36</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000175</v>
+        <v>115000184</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.07.20</t>
+          <t>115.07.30</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>10  12  13  20  24</t>
+          <t>04  07  08  16  38</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000174</v>
+        <v>115000185</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.07.18</t>
+          <t>115.07.31</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>18  29  33  34  37</t>
+          <t>01  09  12  25  26</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000173</v>
+        <v>115000186</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.07.17</t>
+          <t>115.08.01</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>10  12  28  29  35</t>
+          <t>06  11  18  22  29</t>
         </is>
       </c>
     </row>
@@ -1354,169 +1354,183 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000060</v>
+        <v>115000053</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.07.27</t>
+          <t>115.07.02</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>19  22  28  31  33  35</t>
+          <t>02  11  13  21  22  35</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>03</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000059</v>
+        <v>115000054</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.07.23</t>
+          <t>115.07.06</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>08  10  13  21  29  31</t>
+          <t>04  12  15  24  30  31</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>01</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000058</v>
+        <v>115000055</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.07.20</t>
+          <t>115.07.09</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>06  12  13  23  29  31</t>
+          <t>10  22  24  29  35  37</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000057</v>
+        <v>115000056</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.07.16</t>
+          <t>115.07.13</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>17  23  25  29  34  36</t>
+          <t>11  24  29  32  35  38</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.07.13</t>
+          <t>115.07.16</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>11  24  29  32  35  38</t>
+          <t>17  23  25  29  34  36</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000055</v>
+        <v>115000058</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.07.09</t>
+          <t>115.07.20</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>10  22  24  29  35  37</t>
+          <t>06  12  13  23  29  31</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000054</v>
+        <v>115000059</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.07.06</t>
+          <t>115.07.23</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>04  12  15  24  30  31</t>
+          <t>08  10  13  21  29  31</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000053</v>
+        <v>115000060</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.07.02</t>
+          <t>115.07.27</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>02  11  13  21  22  35</t>
+          <t>19  22  28  31  33  35</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
-      <c r="A10" s="4" t="n"/>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
+      <c r="A10" s="4" t="n">
+        <v>115000061</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>115.07.30</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>08  14  17  19  21  23</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n"/>
@@ -1761,169 +1775,183 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000074</v>
+        <v>115000067</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.07.28</t>
+          <t>115.07.03</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>08  19  24  26  32  43</t>
+          <t>11  16  19  23  39  47</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000073</v>
+        <v>115000068</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.07.24</t>
+          <t>115.07.07</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>03  15  27  34  35  44</t>
+          <t>08  13  15  18  19  42</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000072</v>
+        <v>115000069</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.07.21</t>
+          <t>115.07.10</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>02  08  15  26  35  46</t>
+          <t>03  04  15  18  29  49</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000071</v>
+        <v>115000070</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.07.17</t>
+          <t>115.07.14</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>01  06  12  14  17  26</t>
+          <t>10  25  34  36  45  46</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000070</v>
+        <v>115000071</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.07.14</t>
+          <t>115.07.17</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>10  25  34  36  45  46</t>
+          <t>01  06  12  14  17  26</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000069</v>
+        <v>115000072</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.07.10</t>
+          <t>115.07.21</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>03  04  15  18  29  49</t>
+          <t>02  08  15  26  35  46</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000068</v>
+        <v>115000073</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.07.07</t>
+          <t>115.07.24</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>08  13  15  18  19  42</t>
+          <t>03  15  27  34  35  44</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000067</v>
+        <v>115000074</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.07.03</t>
+          <t>115.07.28</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>11  16  19  23  39  47</t>
+          <t>08  19  24  26  32  43</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>47</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
-      <c r="A10" s="4" t="n"/>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
+      <c r="A10" s="4" t="n">
+        <v>115000075</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>115.07.31</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>11  20  23  33  34  44</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n"/>
@@ -2158,120 +2186,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>07/28(二)</t>
+          <t>07/22(三)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>7  1  6</t>
+          <t>5  0  2</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>07/27(一)</t>
+          <t>07/23(四)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>6  0  2</t>
+          <t>0  1  8</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>07/25(六)</t>
+          <t>07/24(五)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>1  8  3</t>
+          <t>5  4  0</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>07/24(五)</t>
+          <t>07/25(六)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>5  4  0</t>
+          <t>1  8  3</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>07/23(四)</t>
+          <t>07/27(一)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>0  1  8</t>
+          <t>6  0  2</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>07/22(三)</t>
+          <t>07/28(二)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>5  0  2</t>
+          <t>7  1  6</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>07/21(二)</t>
+          <t>07/29(三)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>4  1  8</t>
+          <t>8  4  6</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>07/20(一)</t>
+          <t>07/30(四)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>3  0  1</t>
+          <t>2  8  5</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>07/18(六)</t>
+          <t>07/31(五)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>6  6  7</t>
+          <t>1  3  9</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>07/17(五)</t>
+          <t>08/01(六)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>4  1  3</t>
+          <t>5  6  6</t>
         </is>
       </c>
     </row>
@@ -2504,24 +2532,24 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>07/27(一)</t>
+          <t>07/22(三)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>5  9  1  0</t>
+          <t>7  9  4  7</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>07/25(六)</t>
+          <t>07/23(四)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>9  0  4  8</t>
+          <t>5  3  5  1</t>
         </is>
       </c>
     </row>
@@ -2540,48 +2568,48 @@
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>07/23(四)</t>
+          <t>07/25(六)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>5  3  5  1</t>
+          <t>9  0  4  8</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>07/22(三)</t>
+          <t>07/27(一)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>7  9  4  7</t>
+          <t>5  9  1  0</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>07/21(二)</t>
+          <t>07/28(二)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>0  7  5  7</t>
+          <t>0  4  3  3</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>07/20(一)</t>
+          <t>07/29(三)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>4  0  1  4</t>
+          <t>7  6  8  5</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2589,36 +2617,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>07/18(六)</t>
+          <t>07/30(四)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>7  9  9  5</t>
+          <t>2  9  3  1</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>07/17(五)</t>
+          <t>07/31(五)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>7  4  2  0</t>
+          <t>7  1  9  8</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>07/16(四)</t>
+          <t>08/01(六)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>6  4  2  7</t>
+          <t>7  1  9  5</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -2186,120 +2186,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>07/22(三)</t>
+          <t>07/21(二)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>5  0  2</t>
+          <t>4  1  8</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>07/23(四)</t>
+          <t>07/22(三)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>0  1  8</t>
+          <t>5  0  2</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>07/24(五)</t>
+          <t>07/23(四)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>5  4  0</t>
+          <t>0  1  8</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>07/25(六)</t>
+          <t>07/24(五)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>1  8  3</t>
+          <t>5  4  0</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>07/27(一)</t>
+          <t>07/25(六)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>6  0  2</t>
+          <t>1  8  3</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>07/28(二)</t>
+          <t>07/27(一)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>7  1  6</t>
+          <t>6  0  2</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>07/29(三)</t>
+          <t>07/28(二)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>8  4  6</t>
+          <t>7  1  6</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>07/30(四)</t>
+          <t>07/29(三)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2  8  5</t>
+          <t>8  4  6</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>07/31(五)</t>
+          <t>07/30(四)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>1  3  9</t>
+          <t>2  8  5</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>08/01(六)</t>
+          <t>07/31(五)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>5  6  6</t>
+          <t>1  3  9</t>
         </is>
       </c>
     </row>
@@ -2532,84 +2532,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>07/22(三)</t>
+          <t>07/21(二)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>7  9  4  7</t>
+          <t>0  7  5  7</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>07/23(四)</t>
+          <t>07/22(三)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>5  3  5  1</t>
+          <t>7  9  4  7</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>07/24(五)</t>
+          <t>07/23(四)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>3  1  0  8</t>
+          <t>5  3  5  1</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>07/25(六)</t>
+          <t>07/24(五)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>9  0  4  8</t>
+          <t>3  1  0  8</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>07/27(一)</t>
+          <t>07/25(六)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>5  9  1  0</t>
+          <t>9  0  4  8</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>07/28(二)</t>
+          <t>07/27(一)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>0  4  3  3</t>
+          <t>5  9  1  0</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>07/29(三)</t>
+          <t>07/28(二)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>7  6  8  5</t>
+          <t>0  4  3  3</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2617,36 +2617,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>07/30(四)</t>
+          <t>07/29(三)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2  9  3  1</t>
+          <t>7  6  8  5</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>07/31(五)</t>
+          <t>07/30(四)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>7  1  9  8</t>
+          <t>2  9  3  1</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/01(六)</t>
+          <t>07/31(五)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>7  1  9  5</t>
+          <t>7  1  9  8</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -2186,120 +2186,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>07/21(二)</t>
+          <t>07/22(三)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>4  1  8</t>
+          <t>5  0  2</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>07/22(三)</t>
+          <t>07/23(四)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>5  0  2</t>
+          <t>0  1  8</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>07/23(四)</t>
+          <t>07/24(五)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>0  1  8</t>
+          <t>5  4  0</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>07/24(五)</t>
+          <t>07/25(六)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>5  4  0</t>
+          <t>1  8  3</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>07/25(六)</t>
+          <t>07/27(一)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>1  8  3</t>
+          <t>6  0  2</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>07/27(一)</t>
+          <t>07/28(二)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>6  0  2</t>
+          <t>7  1  6</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>07/28(二)</t>
+          <t>07/29(三)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>7  1  6</t>
+          <t>8  4  6</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>07/29(三)</t>
+          <t>07/30(四)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>8  4  6</t>
+          <t>2  8  5</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>07/30(四)</t>
+          <t>07/31(五)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>2  8  5</t>
+          <t>1  3  9</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>07/31(五)</t>
+          <t>08/01(六)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>1  3  9</t>
+          <t>5  6  6</t>
         </is>
       </c>
     </row>
@@ -2532,84 +2532,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>07/21(二)</t>
+          <t>07/22(三)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>0  7  5  7</t>
+          <t>7  9  4  7</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>07/22(三)</t>
+          <t>07/23(四)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>7  9  4  7</t>
+          <t>5  3  5  1</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>07/23(四)</t>
+          <t>07/24(五)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>5  3  5  1</t>
+          <t>3  1  0  8</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>07/24(五)</t>
+          <t>07/25(六)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>3  1  0  8</t>
+          <t>9  0  4  8</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>07/25(六)</t>
+          <t>07/27(一)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>9  0  4  8</t>
+          <t>5  9  1  0</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>07/27(一)</t>
+          <t>07/28(二)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>5  9  1  0</t>
+          <t>0  4  3  3</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>07/28(二)</t>
+          <t>07/29(三)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>0  4  3  3</t>
+          <t>7  6  8  5</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2617,36 +2617,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>07/29(三)</t>
+          <t>07/30(四)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>7  6  8  5</t>
+          <t>2  9  3  1</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>07/30(四)</t>
+          <t>07/31(五)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2  9  3  1</t>
+          <t>7  1  9  8</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>07/31(五)</t>
+          <t>08/01(六)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>7  1  9  8</t>
+          <t>7  1  9  5</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000184</v>
+        <v>115000177</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.07.30</t>
+          <t>115.07.22</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>04  07  08  16  38</t>
+          <t>03  14  19  21  31</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000183</v>
+        <v>115000178</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.07.29</t>
+          <t>115.07.23</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>05  14  32  33  36</t>
+          <t>12  14  19  25  26</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000182</v>
+        <v>115000179</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.07.28</t>
+          <t>115.07.24</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>05  08  13  23  31</t>
+          <t>05  17  27  29  36</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000181</v>
+        <v>115000180</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.07.27</t>
+          <t>115.07.25</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>07  16  19  24  32</t>
+          <t>08  12  16  23  39</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000180</v>
+        <v>115000181</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.07.25</t>
+          <t>115.07.27</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>08  12  16  23  39</t>
+          <t>07  16  19  24  32</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000179</v>
+        <v>115000182</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.07.24</t>
+          <t>115.07.28</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>05  17  27  29  36</t>
+          <t>05  08  13  23  31</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000178</v>
+        <v>115000183</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.07.23</t>
+          <t>115.07.29</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>12  14  19  25  26</t>
+          <t>05  14  32  33  36</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000177</v>
+        <v>115000184</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.07.22</t>
+          <t>115.07.30</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>03  14  19  21  31</t>
+          <t>04  07  08  16  38</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000176</v>
+        <v>115000185</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.07.21</t>
+          <t>115.07.31</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>12  19  27  37  39</t>
+          <t>01  09  12  25  26</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000175</v>
+        <v>115000186</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.07.20</t>
+          <t>115.08.01</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>10  12  13  20  24</t>
+          <t>06  11  18  22  29</t>
         </is>
       </c>
     </row>
@@ -1354,81 +1354,81 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000061</v>
+        <v>115000053</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.07.30</t>
+          <t>115.07.02</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>08  14  17  19  21  23</t>
+          <t>02  11  13  21  22  35</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>03</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000060</v>
+        <v>115000054</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.07.27</t>
+          <t>115.07.06</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>19  22  28  31  33  35</t>
+          <t>04  12  15  24  30  31</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>01</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000059</v>
+        <v>115000055</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.07.23</t>
+          <t>115.07.09</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>08  10  13  21  29  31</t>
+          <t>10  22  24  29  35  37</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000058</v>
+        <v>115000056</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.07.20</t>
+          <t>115.07.13</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>06  12  13  23  29  31</t>
+          <t>11  24  29  32  35  38</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>06</t>
         </is>
       </c>
     </row>
@@ -1454,81 +1454,81 @@
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000056</v>
+        <v>115000058</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.07.13</t>
+          <t>115.07.20</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>11  24  29  32  35  38</t>
+          <t>06  12  13  23  29  31</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000055</v>
+        <v>115000059</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.07.09</t>
+          <t>115.07.23</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>10  22  24  29  35  37</t>
+          <t>08  10  13  21  29  31</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000054</v>
+        <v>115000060</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.07.06</t>
+          <t>115.07.27</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>04  12  15  24  30  31</t>
+          <t>19  22  28  31  33  35</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000053</v>
+        <v>115000061</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.07.02</t>
+          <t>115.07.30</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>02  11  13  21  22  35</t>
+          <t>08  14  17  19  21  23</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>07</t>
         </is>
       </c>
     </row>
@@ -1775,169 +1775,183 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000074</v>
+        <v>115000067</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.07.28</t>
+          <t>115.07.03</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>08  19  24  26  32  43</t>
+          <t>11  16  19  23  39  47</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000073</v>
+        <v>115000068</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.07.24</t>
+          <t>115.07.07</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>03  15  27  34  35  44</t>
+          <t>08  13  15  18  19  42</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000072</v>
+        <v>115000069</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.07.21</t>
+          <t>115.07.10</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>02  08  15  26  35  46</t>
+          <t>03  04  15  18  29  49</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000071</v>
+        <v>115000070</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.07.17</t>
+          <t>115.07.14</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>01  06  12  14  17  26</t>
+          <t>10  25  34  36  45  46</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000070</v>
+        <v>115000071</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.07.14</t>
+          <t>115.07.17</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>10  25  34  36  45  46</t>
+          <t>01  06  12  14  17  26</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000069</v>
+        <v>115000072</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.07.10</t>
+          <t>115.07.21</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>03  04  15  18  29  49</t>
+          <t>02  08  15  26  35  46</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000068</v>
+        <v>115000073</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.07.07</t>
+          <t>115.07.24</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>08  13  15  18  19  42</t>
+          <t>03  15  27  34  35  44</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000067</v>
+        <v>115000074</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.07.03</t>
+          <t>115.07.28</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>11  16  19  23  39  47</t>
+          <t>08  19  24  26  32  43</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>47</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
-      <c r="A10" s="4" t="n"/>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
+      <c r="A10" s="4" t="n">
+        <v>115000075</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>115.07.31</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>11  20  23  33  34  44</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n"/>
@@ -2172,36 +2186,36 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>07/29(三)</t>
+          <t>07/22(三)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>8  4  6</t>
+          <t>5  0  2</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>07/28(二)</t>
+          <t>07/23(四)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>7  1  6</t>
+          <t>0  1  8</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>07/27(一)</t>
+          <t>07/24(五)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>6  0  2</t>
+          <t>5  4  0</t>
         </is>
       </c>
     </row>
@@ -2220,72 +2234,72 @@
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>07/24(五)</t>
+          <t>07/27(一)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>5  4  0</t>
+          <t>6  0  2</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>07/23(四)</t>
+          <t>07/28(二)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>0  1  8</t>
+          <t>7  1  6</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>07/22(三)</t>
+          <t>07/29(三)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>5  0  2</t>
+          <t>8  4  6</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>07/21(二)</t>
+          <t>07/30(四)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>4  1  8</t>
+          <t>2  8  5</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>07/20(一)</t>
+          <t>07/31(五)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>3  0  1</t>
+          <t>1  3  9</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>07/18(六)</t>
+          <t>08/01(六)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>6  6  7</t>
+          <t>5  6  6</t>
         </is>
       </c>
     </row>
@@ -2518,36 +2532,36 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>07/29(三)</t>
+          <t>07/22(三)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>7  6  8  5</t>
+          <t>7  9  4  7</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>07/28(二)</t>
+          <t>07/23(四)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>0  4  3  3</t>
+          <t>5  3  5  1</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>07/27(一)</t>
+          <t>07/24(五)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>5  9  1  0</t>
+          <t>3  1  0  8</t>
         </is>
       </c>
     </row>
@@ -2566,36 +2580,36 @@
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>07/24(五)</t>
+          <t>07/27(一)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>3  1  0  8</t>
+          <t>5  9  1  0</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>07/23(四)</t>
+          <t>07/28(二)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>5  3  5  1</t>
+          <t>0  4  3  3</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>07/22(三)</t>
+          <t>07/29(三)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>7  9  4  7</t>
+          <t>7  6  8  5</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2603,36 +2617,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>07/21(二)</t>
+          <t>07/30(四)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>0  7  5  7</t>
+          <t>2  9  3  1</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>07/20(一)</t>
+          <t>07/31(五)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>4  0  1  4</t>
+          <t>7  1  9  8</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>07/18(六)</t>
+          <t>08/01(六)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>7  9  9  5</t>
+          <t>7  1  9  5</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000177</v>
+        <v>115000178</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.07.22</t>
+          <t>115.07.23</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>03  14  19  21  31</t>
+          <t>12  14  19  25  26</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000178</v>
+        <v>115000179</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.07.23</t>
+          <t>115.07.24</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>12  14  19  25  26</t>
+          <t>05  17  27  29  36</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000179</v>
+        <v>115000180</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.07.24</t>
+          <t>115.07.25</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>05  17  27  29  36</t>
+          <t>08  12  16  23  39</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000180</v>
+        <v>115000181</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.07.25</t>
+          <t>115.07.27</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>08  12  16  23  39</t>
+          <t>07  16  19  24  32</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000181</v>
+        <v>115000182</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.07.27</t>
+          <t>115.07.28</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>07  16  19  24  32</t>
+          <t>05  08  13  23  31</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000182</v>
+        <v>115000183</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.07.28</t>
+          <t>115.07.29</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>05  08  13  23  31</t>
+          <t>05  14  32  33  36</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000183</v>
+        <v>115000184</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.07.29</t>
+          <t>115.07.30</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>05  14  32  33  36</t>
+          <t>04  07  08  16  38</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000184</v>
+        <v>115000185</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.07.30</t>
+          <t>115.07.31</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>04  07  08  16  38</t>
+          <t>01  09  12  25  26</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000185</v>
+        <v>115000186</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.07.31</t>
+          <t>115.08.01</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>01  09  12  25  26</t>
+          <t>06  11  18  22  29</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000186</v>
+        <v>115000187</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.08.01</t>
+          <t>115.08.03</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>06  11  18  22  29</t>
+          <t>07  21  23  28  35</t>
         </is>
       </c>
     </row>
@@ -1533,10 +1533,24 @@
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
-      <c r="A11" s="4" t="n"/>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
+      <c r="A11" s="4" t="n">
+        <v>115000062</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>115.08.03</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>04  15  22  26  34  36</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
     </row>
     <row r="12"/>
     <row r="13"/>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -2200,120 +2200,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>07/22(三)</t>
+          <t>07/23(四)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>5  0  2</t>
+          <t>0  1  8</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>07/23(四)</t>
+          <t>07/24(五)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>0  1  8</t>
+          <t>5  4  0</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>07/24(五)</t>
+          <t>07/25(六)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>5  4  0</t>
+          <t>1  8  3</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>07/25(六)</t>
+          <t>07/27(一)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>1  8  3</t>
+          <t>6  0  2</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>07/27(一)</t>
+          <t>07/28(二)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>6  0  2</t>
+          <t>7  1  6</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>07/28(二)</t>
+          <t>07/29(三)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>7  1  6</t>
+          <t>8  4  6</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>07/29(三)</t>
+          <t>07/30(四)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>8  4  6</t>
+          <t>2  8  5</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>07/30(四)</t>
+          <t>07/31(五)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2  8  5</t>
+          <t>1  3  9</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>07/31(五)</t>
+          <t>08/01(六)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>1  3  9</t>
+          <t>5  6  6</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>08/01(六)</t>
+          <t>08/03(一)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>5  6  6</t>
+          <t>4  9  1</t>
         </is>
       </c>
     </row>
@@ -2546,84 +2546,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>07/22(三)</t>
+          <t>07/23(四)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>7  9  4  7</t>
+          <t>5  3  5  1</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>07/23(四)</t>
+          <t>07/24(五)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>5  3  5  1</t>
+          <t>3  1  0  8</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>07/24(五)</t>
+          <t>07/25(六)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>3  1  0  8</t>
+          <t>9  0  4  8</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>07/25(六)</t>
+          <t>07/27(一)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>9  0  4  8</t>
+          <t>5  9  1  0</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>07/27(一)</t>
+          <t>07/28(二)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>5  9  1  0</t>
+          <t>0  4  3  3</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>07/28(二)</t>
+          <t>07/29(三)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>0  4  3  3</t>
+          <t>7  6  8  5</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>07/29(三)</t>
+          <t>07/30(四)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>7  6  8  5</t>
+          <t>2  9  3  1</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2631,36 +2631,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>07/30(四)</t>
+          <t>07/31(五)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2  9  3  1</t>
+          <t>7  1  9  8</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>07/31(五)</t>
+          <t>08/01(六)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>7  1  9  8</t>
+          <t>7  1  9  5</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/01(六)</t>
+          <t>08/03(一)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>7  1  9  5</t>
+          <t>6  0  1  6</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -2200,120 +2200,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>07/23(四)</t>
+          <t>07/22(三)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>0  1  8</t>
+          <t>5  0  2</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>07/24(五)</t>
+          <t>07/23(四)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>5  4  0</t>
+          <t>0  1  8</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>07/25(六)</t>
+          <t>07/24(五)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>1  8  3</t>
+          <t>5  4  0</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>07/27(一)</t>
+          <t>07/25(六)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>6  0  2</t>
+          <t>1  8  3</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>07/28(二)</t>
+          <t>07/27(一)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>7  1  6</t>
+          <t>6  0  2</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>07/29(三)</t>
+          <t>07/28(二)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>8  4  6</t>
+          <t>7  1  6</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>07/30(四)</t>
+          <t>07/29(三)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>2  8  5</t>
+          <t>8  4  6</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>07/31(五)</t>
+          <t>07/30(四)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>1  3  9</t>
+          <t>2  8  5</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>08/01(六)</t>
+          <t>07/31(五)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>5  6  6</t>
+          <t>1  3  9</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>08/03(一)</t>
+          <t>08/01(六)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>4  9  1</t>
+          <t>5  6  6</t>
         </is>
       </c>
     </row>
@@ -2546,84 +2546,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>07/23(四)</t>
+          <t>07/22(三)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>5  3  5  1</t>
+          <t>7  9  4  7</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>07/24(五)</t>
+          <t>07/23(四)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>3  1  0  8</t>
+          <t>5  3  5  1</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>07/25(六)</t>
+          <t>07/24(五)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>9  0  4  8</t>
+          <t>3  1  0  8</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>07/27(一)</t>
+          <t>07/25(六)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>5  9  1  0</t>
+          <t>9  0  4  8</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>07/28(二)</t>
+          <t>07/27(一)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>0  4  3  3</t>
+          <t>5  9  1  0</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>07/29(三)</t>
+          <t>07/28(二)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>7  6  8  5</t>
+          <t>0  4  3  3</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>07/30(四)</t>
+          <t>07/29(三)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2  9  3  1</t>
+          <t>7  6  8  5</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2631,36 +2631,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>07/31(五)</t>
+          <t>07/30(四)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>7  1  9  8</t>
+          <t>2  9  3  1</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/01(六)</t>
+          <t>07/31(五)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>7  1  9  5</t>
+          <t>7  1  9  8</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/03(一)</t>
+          <t>08/01(六)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>6  0  1  6</t>
+          <t>7  1  9  5</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000178</v>
+        <v>115000179</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.07.23</t>
+          <t>115.07.24</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>12  14  19  25  26</t>
+          <t>05  17  27  29  36</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000179</v>
+        <v>115000180</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.07.24</t>
+          <t>115.07.25</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>05  17  27  29  36</t>
+          <t>08  12  16  23  39</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000180</v>
+        <v>115000181</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.07.25</t>
+          <t>115.07.27</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>08  12  16  23  39</t>
+          <t>07  16  19  24  32</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000181</v>
+        <v>115000182</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.07.27</t>
+          <t>115.07.28</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>07  16  19  24  32</t>
+          <t>05  08  13  23  31</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000182</v>
+        <v>115000183</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.07.28</t>
+          <t>115.07.29</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>05  08  13  23  31</t>
+          <t>05  14  32  33  36</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000183</v>
+        <v>115000184</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.07.29</t>
+          <t>115.07.30</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>05  14  32  33  36</t>
+          <t>04  07  08  16  38</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000184</v>
+        <v>115000185</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.07.30</t>
+          <t>115.07.31</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>04  07  08  16  38</t>
+          <t>01  09  12  25  26</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000185</v>
+        <v>115000186</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.07.31</t>
+          <t>115.08.01</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>01  09  12  25  26</t>
+          <t>06  11  18  22  29</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000186</v>
+        <v>115000187</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.08.01</t>
+          <t>115.08.03</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>06  11  18  22  29</t>
+          <t>07  21  23  28  35</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000187</v>
+        <v>115000188</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.08.03</t>
+          <t>115.08.04</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>07  21  23  28  35</t>
+          <t>09  32  35  37  39</t>
         </is>
       </c>
     </row>
@@ -1968,10 +1968,24 @@
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
-      <c r="A11" s="4" t="n"/>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
+      <c r="A11" s="4" t="n">
+        <v>115000076</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>115.08.04</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>04  09  15  30  36  49</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
     </row>
     <row r="12"/>
     <row r="13"/>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>07/23(四)</t>
+          <t>07/22(三)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>5  3  5  1</t>
+          <t>7  9  4  7</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>07/24(五)</t>
+          <t>07/23(四)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>3  1  0  8</t>
+          <t>5  3  5  1</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>07/25(六)</t>
+          <t>07/24(五)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>9  0  4  8</t>
+          <t>3  1  0  8</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>07/27(一)</t>
+          <t>07/25(六)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>5  9  1  0</t>
+          <t>9  0  4  8</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>07/28(二)</t>
+          <t>07/27(一)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>0  4  3  3</t>
+          <t>5  9  1  0</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>07/29(三)</t>
+          <t>07/28(二)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>7  6  8  5</t>
+          <t>0  4  3  3</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>07/30(四)</t>
+          <t>07/29(三)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2  9  3  1</t>
+          <t>7  6  8  5</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>07/31(五)</t>
+          <t>07/30(四)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>7  1  9  8</t>
+          <t>2  9  3  1</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/01(六)</t>
+          <t>07/31(五)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>7  1  9  5</t>
+          <t>7  1  9  8</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/03(一)</t>
+          <t>08/01(六)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>6  0  1  6</t>
+          <t>7  1  9  5</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>07/22(三)</t>
+          <t>07/23(四)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>7  9  4  7</t>
+          <t>5  3  5  1</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>07/23(四)</t>
+          <t>07/24(五)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>5  3  5  1</t>
+          <t>3  1  0  8</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>07/24(五)</t>
+          <t>07/25(六)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>3  1  0  8</t>
+          <t>9  0  4  8</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>07/25(六)</t>
+          <t>07/27(一)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>9  0  4  8</t>
+          <t>5  9  1  0</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>07/27(一)</t>
+          <t>07/28(二)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>5  9  1  0</t>
+          <t>0  4  3  3</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>07/28(二)</t>
+          <t>07/29(三)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>0  4  3  3</t>
+          <t>7  6  8  5</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>07/29(三)</t>
+          <t>07/30(四)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>7  6  8  5</t>
+          <t>2  9  3  1</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>07/30(四)</t>
+          <t>07/31(五)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2  9  3  1</t>
+          <t>7  1  9  8</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>07/31(五)</t>
+          <t>08/01(六)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>7  1  9  8</t>
+          <t>7  1  9  5</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/01(六)</t>
+          <t>08/03(一)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>7  1  9  5</t>
+          <t>6  0  1  6</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>07/23(四)</t>
+          <t>07/22(三)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>0  1  8</t>
+          <t>5  0  2</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>07/24(五)</t>
+          <t>07/23(四)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>5  4  0</t>
+          <t>0  1  8</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>07/25(六)</t>
+          <t>07/24(五)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>1  8  3</t>
+          <t>5  4  0</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>07/27(一)</t>
+          <t>07/25(六)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>6  0  2</t>
+          <t>1  8  3</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>07/28(二)</t>
+          <t>07/27(一)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>7  1  6</t>
+          <t>6  0  2</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>07/29(三)</t>
+          <t>07/28(二)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>8  4  6</t>
+          <t>7  1  6</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>07/30(四)</t>
+          <t>07/29(三)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>2  8  5</t>
+          <t>8  4  6</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>07/31(五)</t>
+          <t>07/30(四)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>1  3  9</t>
+          <t>2  8  5</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>08/01(六)</t>
+          <t>07/31(五)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>5  6  6</t>
+          <t>1  3  9</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>08/03(一)</t>
+          <t>08/01(六)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>4  9  1</t>
+          <t>5  6  6</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000177</v>
+        <v>115000179</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.07.22</t>
+          <t>115.07.24</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>03  14  19  21  31</t>
+          <t>05  17  27  29  36</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000178</v>
+        <v>115000180</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.07.23</t>
+          <t>115.07.25</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>12  14  19  25  26</t>
+          <t>08  12  16  23  39</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000179</v>
+        <v>115000181</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.07.24</t>
+          <t>115.07.27</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>05  17  27  29  36</t>
+          <t>07  16  19  24  32</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000180</v>
+        <v>115000182</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.07.25</t>
+          <t>115.07.28</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>08  12  16  23  39</t>
+          <t>05  08  13  23  31</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000181</v>
+        <v>115000183</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.07.27</t>
+          <t>115.07.29</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>07  16  19  24  32</t>
+          <t>05  14  32  33  36</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000182</v>
+        <v>115000184</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.07.28</t>
+          <t>115.07.30</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>05  08  13  23  31</t>
+          <t>04  07  08  16  38</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000183</v>
+        <v>115000185</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.07.29</t>
+          <t>115.07.31</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>05  14  32  33  36</t>
+          <t>01  09  12  25  26</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000184</v>
+        <v>115000186</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.07.30</t>
+          <t>115.08.01</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>04  07  08  16  38</t>
+          <t>06  11  18  22  29</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000185</v>
+        <v>115000187</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.07.31</t>
+          <t>115.08.03</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>01  09  12  25  26</t>
+          <t>07  21  23  28  35</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000186</v>
+        <v>115000188</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.08.01</t>
+          <t>115.08.04</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>06  11  18  22  29</t>
+          <t>09  32  35  37  39</t>
         </is>
       </c>
     </row>
@@ -1533,10 +1533,24 @@
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
-      <c r="A11" s="4" t="n"/>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
+      <c r="A11" s="4" t="n">
+        <v>115000062</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>115.08.03</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>04  15  22  26  34  36</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
     </row>
     <row r="12"/>
     <row r="13"/>
@@ -1954,10 +1968,24 @@
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
-      <c r="A11" s="4" t="n"/>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
+      <c r="A11" s="4" t="n">
+        <v>115000076</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>115.08.04</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>04  09  15  30  36  49</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
     </row>
     <row r="12"/>
     <row r="13"/>
@@ -2186,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>07/22(三)</t>
+          <t>07/23(四)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>5  0  2</t>
+          <t>0  1  8</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>07/23(四)</t>
+          <t>07/24(五)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>0  1  8</t>
+          <t>5  4  0</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>07/24(五)</t>
+          <t>07/25(六)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>5  4  0</t>
+          <t>1  8  3</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>07/25(六)</t>
+          <t>07/27(一)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>1  8  3</t>
+          <t>6  0  2</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>07/27(一)</t>
+          <t>07/28(二)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>6  0  2</t>
+          <t>7  1  6</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>07/28(二)</t>
+          <t>07/29(三)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>7  1  6</t>
+          <t>8  4  6</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>07/29(三)</t>
+          <t>07/30(四)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>8  4  6</t>
+          <t>2  8  5</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>07/30(四)</t>
+          <t>07/31(五)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2  8  5</t>
+          <t>1  3  9</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>07/31(五)</t>
+          <t>08/01(六)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>1  3  9</t>
+          <t>5  6  6</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>08/01(六)</t>
+          <t>08/03(一)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>5  6  6</t>
+          <t>4  9  1</t>
         </is>
       </c>
     </row>
@@ -2532,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>07/22(三)</t>
+          <t>07/23(四)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>7  9  4  7</t>
+          <t>5  3  5  1</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>07/23(四)</t>
+          <t>07/24(五)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>5  3  5  1</t>
+          <t>3  1  0  8</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>07/24(五)</t>
+          <t>07/25(六)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>3  1  0  8</t>
+          <t>9  0  4  8</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>07/25(六)</t>
+          <t>07/27(一)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>9  0  4  8</t>
+          <t>5  9  1  0</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>07/27(一)</t>
+          <t>07/28(二)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>5  9  1  0</t>
+          <t>0  4  3  3</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>07/28(二)</t>
+          <t>07/29(三)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>0  4  3  3</t>
+          <t>7  6  8  5</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>07/29(三)</t>
+          <t>07/30(四)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>7  6  8  5</t>
+          <t>2  9  3  1</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2617,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>07/30(四)</t>
+          <t>07/31(五)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2  9  3  1</t>
+          <t>7  1  9  8</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>07/31(五)</t>
+          <t>08/01(六)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>7  1  9  8</t>
+          <t>7  1  9  5</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/01(六)</t>
+          <t>08/03(一)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>7  1  9  5</t>
+          <t>6  0  1  6</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>07/22(三)</t>
+          <t>07/24(五)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>5  0  2</t>
+          <t>5  4  0</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>07/23(四)</t>
+          <t>07/25(六)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>0  1  8</t>
+          <t>1  8  3</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>07/24(五)</t>
+          <t>07/27(一)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>5  4  0</t>
+          <t>6  0  2</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>07/25(六)</t>
+          <t>07/28(二)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>1  8  3</t>
+          <t>7  1  6</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>07/27(一)</t>
+          <t>07/29(三)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>6  0  2</t>
+          <t>8  4  6</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>07/28(二)</t>
+          <t>07/30(四)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>7  1  6</t>
+          <t>2  8  5</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>07/29(三)</t>
+          <t>07/31(五)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>8  4  6</t>
+          <t>1  3  9</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>07/30(四)</t>
+          <t>08/01(六)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2  8  5</t>
+          <t>5  6  6</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>07/31(五)</t>
+          <t>08/03(一)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>1  3  9</t>
+          <t>4  9  1</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>08/01(六)</t>
+          <t>08/04(二)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>5  6  6</t>
+          <t>9  9  1</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>07/23(四)</t>
+          <t>07/24(五)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>5  3  5  1</t>
+          <t>3  1  0  8</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>07/24(五)</t>
+          <t>07/25(六)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>3  1  0  8</t>
+          <t>9  0  4  8</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>07/25(六)</t>
+          <t>07/27(一)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>9  0  4  8</t>
+          <t>5  9  1  0</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>07/27(一)</t>
+          <t>07/28(二)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>5  9  1  0</t>
+          <t>0  4  3  3</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>07/28(二)</t>
+          <t>07/29(三)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>0  4  3  3</t>
+          <t>7  6  8  5</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>07/29(三)</t>
+          <t>07/30(四)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>7  6  8  5</t>
+          <t>2  9  3  1</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>07/30(四)</t>
+          <t>07/31(五)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2  9  3  1</t>
+          <t>7  1  9  8</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>07/31(五)</t>
+          <t>08/01(六)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>7  1  9  8</t>
+          <t>7  1  9  5</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/01(六)</t>
+          <t>08/03(一)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>7  1  9  5</t>
+          <t>6  0  1  6</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/03(一)</t>
+          <t>08/04(二)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>6  0  1  6</t>
+          <t>1  8  4  3</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000179</v>
+        <v>115000180</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.07.24</t>
+          <t>115.07.25</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>05  17  27  29  36</t>
+          <t>08  12  16  23  39</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000180</v>
+        <v>115000181</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.07.25</t>
+          <t>115.07.27</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>08  12  16  23  39</t>
+          <t>07  16  19  24  32</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000181</v>
+        <v>115000182</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.07.27</t>
+          <t>115.07.28</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>07  16  19  24  32</t>
+          <t>05  08  13  23  31</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000182</v>
+        <v>115000183</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.07.28</t>
+          <t>115.07.29</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>05  08  13  23  31</t>
+          <t>05  14  32  33  36</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000183</v>
+        <v>115000184</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.07.29</t>
+          <t>115.07.30</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>05  14  32  33  36</t>
+          <t>04  07  08  16  38</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000184</v>
+        <v>115000185</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.07.30</t>
+          <t>115.07.31</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>04  07  08  16  38</t>
+          <t>01  09  12  25  26</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000185</v>
+        <v>115000186</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.07.31</t>
+          <t>115.08.01</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>01  09  12  25  26</t>
+          <t>06  11  18  22  29</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000186</v>
+        <v>115000187</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.08.01</t>
+          <t>115.08.03</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>06  11  18  22  29</t>
+          <t>07  21  23  28  35</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000187</v>
+        <v>115000188</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.08.03</t>
+          <t>115.08.04</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>07  21  23  28  35</t>
+          <t>09  32  35  37  39</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000188</v>
+        <v>115000189</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.08.04</t>
+          <t>115.08.05</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>09  32  35  37  39</t>
+          <t>02  04  22  25  29</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>07/24(五)</t>
+          <t>07/25(六)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>3  1  0  8</t>
+          <t>9  0  4  8</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>07/25(六)</t>
+          <t>07/27(一)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>9  0  4  8</t>
+          <t>5  9  1  0</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>07/27(一)</t>
+          <t>07/28(二)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>5  9  1  0</t>
+          <t>0  4  3  3</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>07/28(二)</t>
+          <t>07/29(三)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>0  4  3  3</t>
+          <t>7  6  8  5</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>07/29(三)</t>
+          <t>07/30(四)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>7  6  8  5</t>
+          <t>2  9  3  1</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>07/30(四)</t>
+          <t>07/31(五)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2  9  3  1</t>
+          <t>7  1  9  8</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>07/31(五)</t>
+          <t>08/01(六)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>7  1  9  8</t>
+          <t>7  1  9  5</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>08/01(六)</t>
+          <t>08/03(一)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>7  1  9  5</t>
+          <t>6  0  1  6</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/03(一)</t>
+          <t>08/04(二)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>6  0  1  6</t>
+          <t>1  8  4  3</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/04(二)</t>
+          <t>08/05(三)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>1  8  4  3</t>
+          <t>0  8  2  3</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>07/25(六)</t>
+          <t>07/24(五)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>9  0  4  8</t>
+          <t>3  1  0  8</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>07/27(一)</t>
+          <t>07/25(六)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>5  9  1  0</t>
+          <t>9  0  4  8</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>07/28(二)</t>
+          <t>07/27(一)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>0  4  3  3</t>
+          <t>5  9  1  0</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>07/29(三)</t>
+          <t>07/28(二)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>7  6  8  5</t>
+          <t>0  4  3  3</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>07/30(四)</t>
+          <t>07/29(三)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2  9  3  1</t>
+          <t>7  6  8  5</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>07/31(五)</t>
+          <t>07/30(四)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>7  1  9  8</t>
+          <t>2  9  3  1</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>08/01(六)</t>
+          <t>07/31(五)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>7  1  9  5</t>
+          <t>7  1  9  8</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>08/03(一)</t>
+          <t>08/01(六)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>6  0  1  6</t>
+          <t>7  1  9  5</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/04(二)</t>
+          <t>08/03(一)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>1  8  4  3</t>
+          <t>6  0  1  6</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/05(三)</t>
+          <t>08/04(二)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>0  8  2  3</t>
+          <t>1  8  4  3</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>07/24(五)</t>
+          <t>07/25(六)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>5  4  0</t>
+          <t>1  8  3</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>07/25(六)</t>
+          <t>07/27(一)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>1  8  3</t>
+          <t>6  0  2</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>07/27(一)</t>
+          <t>07/28(二)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>6  0  2</t>
+          <t>7  1  6</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>07/28(二)</t>
+          <t>07/29(三)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>7  1  6</t>
+          <t>8  4  6</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>07/29(三)</t>
+          <t>07/30(四)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>8  4  6</t>
+          <t>2  8  5</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>07/30(四)</t>
+          <t>07/31(五)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2  8  5</t>
+          <t>1  3  9</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>07/31(五)</t>
+          <t>08/01(六)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>1  3  9</t>
+          <t>5  6  6</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>08/01(六)</t>
+          <t>08/03(一)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>5  6  6</t>
+          <t>4  9  1</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>08/03(一)</t>
+          <t>08/04(二)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>4  9  1</t>
+          <t>9  9  1</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>08/04(二)</t>
+          <t>08/05(三)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>9  9  1</t>
+          <t>3  1  5</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>07/24(五)</t>
+          <t>07/25(六)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>3  1  0  8</t>
+          <t>9  0  4  8</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>07/25(六)</t>
+          <t>07/27(一)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>9  0  4  8</t>
+          <t>5  9  1  0</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>07/27(一)</t>
+          <t>07/28(二)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>5  9  1  0</t>
+          <t>0  4  3  3</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>07/28(二)</t>
+          <t>07/29(三)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>0  4  3  3</t>
+          <t>7  6  8  5</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>07/29(三)</t>
+          <t>07/30(四)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>7  6  8  5</t>
+          <t>2  9  3  1</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>07/30(四)</t>
+          <t>07/31(五)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2  9  3  1</t>
+          <t>7  1  9  8</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>07/31(五)</t>
+          <t>08/01(六)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>7  1  9  8</t>
+          <t>7  1  9  5</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>08/01(六)</t>
+          <t>08/03(一)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>7  1  9  5</t>
+          <t>6  0  1  6</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/03(一)</t>
+          <t>08/04(二)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>6  0  1  6</t>
+          <t>1  8  4  3</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/04(二)</t>
+          <t>08/05(三)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>1  8  4  3</t>
+          <t>0  8  2  3</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000180</v>
+        <v>115000181</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.07.25</t>
+          <t>115.07.27</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>08  12  16  23  39</t>
+          <t>07  16  19  24  32</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000181</v>
+        <v>115000182</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.07.27</t>
+          <t>115.07.28</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>07  16  19  24  32</t>
+          <t>05  08  13  23  31</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000182</v>
+        <v>115000183</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.07.28</t>
+          <t>115.07.29</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>05  08  13  23  31</t>
+          <t>05  14  32  33  36</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000183</v>
+        <v>115000184</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.07.29</t>
+          <t>115.07.30</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>05  14  32  33  36</t>
+          <t>04  07  08  16  38</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000184</v>
+        <v>115000185</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.07.30</t>
+          <t>115.07.31</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>04  07  08  16  38</t>
+          <t>01  09  12  25  26</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000185</v>
+        <v>115000186</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.07.31</t>
+          <t>115.08.01</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>01  09  12  25  26</t>
+          <t>06  11  18  22  29</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000186</v>
+        <v>115000187</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.08.01</t>
+          <t>115.08.03</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>06  11  18  22  29</t>
+          <t>07  21  23  28  35</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000187</v>
+        <v>115000188</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.08.03</t>
+          <t>115.08.04</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>07  21  23  28  35</t>
+          <t>09  32  35  37  39</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000188</v>
+        <v>115000189</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.08.04</t>
+          <t>115.08.05</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>09  32  35  37  39</t>
+          <t>02  04  22  25  29</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000189</v>
+        <v>115000190</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.08.05</t>
+          <t>115.08.06</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>02  04  22  25  29</t>
+          <t>03  09  16  24  35</t>
         </is>
       </c>
     </row>
@@ -1354,56 +1354,56 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000053</v>
+        <v>115000054</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.07.02</t>
+          <t>115.07.06</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>02  11  13  21  22  35</t>
+          <t>04  12  15  24  30  31</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>01</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000054</v>
+        <v>115000055</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.07.06</t>
+          <t>115.07.09</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>04  12  15  24  30  31</t>
+          <t>10  22  24  29  35  37</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000055</v>
+        <v>115000056</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.07.09</t>
+          <t>115.07.13</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>10  22  24  29  35  37</t>
+          <t>11  24  29  32  35  38</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -1414,76 +1414,76 @@
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.07.13</t>
+          <t>115.07.16</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>11  24  29  32  35  38</t>
+          <t>17  23  25  29  34  36</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.07.16</t>
+          <t>115.07.20</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>17  23  25  29  34  36</t>
+          <t>06  12  13  23  29  31</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.07.20</t>
+          <t>115.07.23</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>06  12  13  23  29  31</t>
+          <t>08  10  13  21  29  31</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.07.23</t>
+          <t>115.07.27</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>08  10  13  21  29  31</t>
+          <t>19  22  28  31  33  35</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -1494,16 +1494,16 @@
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.07.27</t>
+          <t>115.07.30</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>19  22  28  31  33  35</t>
+          <t>08  14  17  19  21  23</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -1514,16 +1514,16 @@
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.07.30</t>
+          <t>115.08.03</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>08  14  17  19  21  23</t>
+          <t>04  15  22  26  34  36</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -1534,21 +1534,21 @@
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.08.03</t>
+          <t>115.08.06</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>04  15  22  26  34  36</t>
+          <t>02  07  08  20  26  33</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>04</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>07/25(六)</t>
+          <t>07/27(一)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>9  0  4  8</t>
+          <t>5  9  1  0</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>07/27(一)</t>
+          <t>07/28(二)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>5  9  1  0</t>
+          <t>0  4  3  3</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>07/28(二)</t>
+          <t>07/29(三)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>0  4  3  3</t>
+          <t>7  6  8  5</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>07/29(三)</t>
+          <t>07/30(四)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>7  6  8  5</t>
+          <t>2  9  3  1</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>07/30(四)</t>
+          <t>07/31(五)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2  9  3  1</t>
+          <t>7  1  9  8</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>07/31(五)</t>
+          <t>08/01(六)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>7  1  9  8</t>
+          <t>7  1  9  5</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>08/01(六)</t>
+          <t>08/03(一)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>7  1  9  5</t>
+          <t>6  0  1  6</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>08/03(一)</t>
+          <t>08/04(二)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>6  0  1  6</t>
+          <t>1  8  4  3</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/04(二)</t>
+          <t>08/05(三)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>1  8  4  3</t>
+          <t>0  8  2  3</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/05(三)</t>
+          <t>08/06(四)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>0  8  2  3</t>
+          <t>6  3  4  5</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000179</v>
+        <v>115000181</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.07.24</t>
+          <t>115.07.27</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>05  17  27  29  36</t>
+          <t>07  16  19  24  32</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000180</v>
+        <v>115000182</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.07.25</t>
+          <t>115.07.28</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>08  12  16  23  39</t>
+          <t>05  08  13  23  31</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000181</v>
+        <v>115000183</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.07.27</t>
+          <t>115.07.29</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>07  16  19  24  32</t>
+          <t>05  14  32  33  36</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000182</v>
+        <v>115000184</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.07.28</t>
+          <t>115.07.30</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>05  08  13  23  31</t>
+          <t>04  07  08  16  38</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000183</v>
+        <v>115000185</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.07.29</t>
+          <t>115.07.31</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>05  14  32  33  36</t>
+          <t>01  09  12  25  26</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000184</v>
+        <v>115000186</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.07.30</t>
+          <t>115.08.01</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>04  07  08  16  38</t>
+          <t>06  11  18  22  29</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000185</v>
+        <v>115000187</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.07.31</t>
+          <t>115.08.03</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>01  09  12  25  26</t>
+          <t>07  21  23  28  35</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000186</v>
+        <v>115000188</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.08.01</t>
+          <t>115.08.04</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>06  11  18  22  29</t>
+          <t>09  32  35  37  39</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000187</v>
+        <v>115000189</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.08.03</t>
+          <t>115.08.05</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>07  21  23  28  35</t>
+          <t>02  04  22  25  29</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000188</v>
+        <v>115000190</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.08.04</t>
+          <t>115.08.06</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>09  32  35  37  39</t>
+          <t>03  09  16  24  35</t>
         </is>
       </c>
     </row>
@@ -1354,56 +1354,56 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000053</v>
+        <v>115000054</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.07.02</t>
+          <t>115.07.06</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>02  11  13  21  22  35</t>
+          <t>04  12  15  24  30  31</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>01</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000054</v>
+        <v>115000055</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.07.06</t>
+          <t>115.07.09</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>04  12  15  24  30  31</t>
+          <t>10  22  24  29  35  37</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000055</v>
+        <v>115000056</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.07.09</t>
+          <t>115.07.13</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>10  22  24  29  35  37</t>
+          <t>11  24  29  32  35  38</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -1414,76 +1414,76 @@
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.07.13</t>
+          <t>115.07.16</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>11  24  29  32  35  38</t>
+          <t>17  23  25  29  34  36</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.07.16</t>
+          <t>115.07.20</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>17  23  25  29  34  36</t>
+          <t>06  12  13  23  29  31</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.07.20</t>
+          <t>115.07.23</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>06  12  13  23  29  31</t>
+          <t>08  10  13  21  29  31</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.07.23</t>
+          <t>115.07.27</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>08  10  13  21  29  31</t>
+          <t>19  22  28  31  33  35</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -1494,16 +1494,16 @@
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.07.27</t>
+          <t>115.07.30</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>19  22  28  31  33  35</t>
+          <t>08  14  17  19  21  23</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -1514,16 +1514,16 @@
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.07.30</t>
+          <t>115.08.03</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>08  14  17  19  21  23</t>
+          <t>04  15  22  26  34  36</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -1534,21 +1534,21 @@
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.08.03</t>
+          <t>115.08.06</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>04  15  22  26  34  36</t>
+          <t>02  07  08  20  26  33</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>04</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>07/23(四)</t>
+          <t>07/25(六)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>0  1  8</t>
+          <t>1  8  3</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>07/24(五)</t>
+          <t>07/27(一)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>5  4  0</t>
+          <t>6  0  2</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>07/25(六)</t>
+          <t>07/28(二)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>1  8  3</t>
+          <t>7  1  6</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>07/27(一)</t>
+          <t>07/29(三)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>6  0  2</t>
+          <t>8  4  6</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>07/28(二)</t>
+          <t>07/30(四)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>7  1  6</t>
+          <t>2  8  5</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>07/29(三)</t>
+          <t>07/31(五)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>8  4  6</t>
+          <t>1  3  9</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>07/30(四)</t>
+          <t>08/01(六)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>2  8  5</t>
+          <t>5  6  6</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>07/31(五)</t>
+          <t>08/03(一)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>1  3  9</t>
+          <t>4  9  1</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>08/01(六)</t>
+          <t>08/04(二)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>5  6  6</t>
+          <t>9  9  1</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>08/03(一)</t>
+          <t>08/05(三)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>4  9  1</t>
+          <t>3  1  5</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>07/22(三)</t>
+          <t>07/25(六)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>7  9  4  7</t>
+          <t>9  0  4  8</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>07/23(四)</t>
+          <t>07/27(一)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>5  3  5  1</t>
+          <t>5  9  1  0</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>07/24(五)</t>
+          <t>07/28(二)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>3  1  0  8</t>
+          <t>0  4  3  3</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>07/25(六)</t>
+          <t>07/29(三)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>9  0  4  8</t>
+          <t>7  6  8  5</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>07/27(一)</t>
+          <t>07/30(四)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>5  9  1  0</t>
+          <t>2  9  3  1</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>07/28(二)</t>
+          <t>07/31(五)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>0  4  3  3</t>
+          <t>7  1  9  8</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>07/29(三)</t>
+          <t>08/01(六)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>7  6  8  5</t>
+          <t>7  1  9  5</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>07/30(四)</t>
+          <t>08/03(一)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2  9  3  1</t>
+          <t>6  0  1  6</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>07/31(五)</t>
+          <t>08/04(二)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>7  1  9  8</t>
+          <t>1  8  4  3</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/01(六)</t>
+          <t>08/05(三)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>7  1  9  5</t>
+          <t>0  8  2  3</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>07/27(一)</t>
+          <t>07/25(六)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>5  9  1  0</t>
+          <t>9  0  4  8</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>07/28(二)</t>
+          <t>07/27(一)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>0  4  3  3</t>
+          <t>5  9  1  0</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>07/29(三)</t>
+          <t>07/28(二)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>7  6  8  5</t>
+          <t>0  4  3  3</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>07/30(四)</t>
+          <t>07/29(三)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2  9  3  1</t>
+          <t>7  6  8  5</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>07/31(五)</t>
+          <t>07/30(四)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>7  1  9  8</t>
+          <t>2  9  3  1</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>08/01(六)</t>
+          <t>07/31(五)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>7  1  9  5</t>
+          <t>7  1  9  8</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>08/03(一)</t>
+          <t>08/01(六)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>6  0  1  6</t>
+          <t>7  1  9  5</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>08/04(二)</t>
+          <t>08/03(一)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>1  8  4  3</t>
+          <t>6  0  1  6</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/05(三)</t>
+          <t>08/04(二)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>0  8  2  3</t>
+          <t>1  8  4  3</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/06(四)</t>
+          <t>08/05(三)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>6  3  4  5</t>
+          <t>0  8  2  3</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000181</v>
+        <v>115000182</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.07.27</t>
+          <t>115.07.28</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>07  16  19  24  32</t>
+          <t>05  08  13  23  31</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000182</v>
+        <v>115000183</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.07.28</t>
+          <t>115.07.29</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>05  08  13  23  31</t>
+          <t>05  14  32  33  36</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000183</v>
+        <v>115000184</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.07.29</t>
+          <t>115.07.30</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>05  14  32  33  36</t>
+          <t>04  07  08  16  38</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000184</v>
+        <v>115000185</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.07.30</t>
+          <t>115.07.31</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>04  07  08  16  38</t>
+          <t>01  09  12  25  26</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000185</v>
+        <v>115000186</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.07.31</t>
+          <t>115.08.01</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>01  09  12  25  26</t>
+          <t>06  11  18  22  29</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000186</v>
+        <v>115000187</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.08.01</t>
+          <t>115.08.03</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>06  11  18  22  29</t>
+          <t>07  21  23  28  35</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000187</v>
+        <v>115000188</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.08.03</t>
+          <t>115.08.04</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>07  21  23  28  35</t>
+          <t>09  32  35  37  39</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000188</v>
+        <v>115000189</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.08.04</t>
+          <t>115.08.05</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>09  32  35  37  39</t>
+          <t>02  04  22  25  29</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000189</v>
+        <v>115000190</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.08.05</t>
+          <t>115.08.06</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>02  04  22  25  29</t>
+          <t>03  09  16  24  35</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000190</v>
+        <v>115000191</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.08.06</t>
+          <t>115.08.07</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>03  09  16  24  35</t>
+          <t>06  11  12  13  19</t>
         </is>
       </c>
     </row>
@@ -1789,201 +1789,201 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000067</v>
+        <v>115000068</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.07.03</t>
+          <t>115.07.07</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>11  16  19  23  39  47</t>
+          <t>08  13  15  18  19  42</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000068</v>
+        <v>115000069</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.07.07</t>
+          <t>115.07.10</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>08  13  15  18  19  42</t>
+          <t>03  04  15  18  29  49</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>13</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000069</v>
+        <v>115000070</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.07.10</t>
+          <t>115.07.14</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>03  04  15  18  29  49</t>
+          <t>10  25  34  36  45  46</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000070</v>
+        <v>115000071</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.07.14</t>
+          <t>115.07.17</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>10  25  34  36  45  46</t>
+          <t>01  06  12  14  17  26</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000071</v>
+        <v>115000072</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.07.17</t>
+          <t>115.07.21</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>01  06  12  14  17  26</t>
+          <t>02  08  15  26  35  46</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000072</v>
+        <v>115000073</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.07.21</t>
+          <t>115.07.24</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>02  08  15  26  35  46</t>
+          <t>03  15  27  34  35  44</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000073</v>
+        <v>115000074</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.07.24</t>
+          <t>115.07.28</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>03  15  27  34  35  44</t>
+          <t>08  19  24  26  32  43</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>47</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000074</v>
+        <v>115000075</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.07.28</t>
+          <t>115.07.31</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>08  19  24  26  32  43</t>
+          <t>11  20  23  33  34  44</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000075</v>
+        <v>115000076</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.07.31</t>
+          <t>115.08.04</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>11  20  23  33  34  44</t>
+          <t>04  09  15  30  36  49</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000076</v>
+        <v>115000077</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.08.04</t>
+          <t>115.08.07</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>04  09  15  30  36  49</t>
+          <t>02  12  19  21  25  41</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>07/25(六)</t>
+          <t>07/27(一)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>1  8  3</t>
+          <t>6  0  2</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>07/27(一)</t>
+          <t>07/28(二)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>6  0  2</t>
+          <t>7  1  6</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>07/28(二)</t>
+          <t>07/29(三)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>7  1  6</t>
+          <t>8  4  6</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>07/29(三)</t>
+          <t>07/30(四)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>8  4  6</t>
+          <t>2  8  5</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>07/30(四)</t>
+          <t>07/31(五)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2  8  5</t>
+          <t>1  3  9</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>07/31(五)</t>
+          <t>08/01(六)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>1  3  9</t>
+          <t>5  6  6</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>08/01(六)</t>
+          <t>08/03(一)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>5  6  6</t>
+          <t>4  9  1</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>08/03(一)</t>
+          <t>08/04(二)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>4  9  1</t>
+          <t>9  9  1</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>08/04(二)</t>
+          <t>08/05(三)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>9  9  1</t>
+          <t>3  1  5</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>08/05(三)</t>
+          <t>08/06(四)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>3  1  5</t>
+          <t>1  0  7</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>07/25(六)</t>
+          <t>07/27(一)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>9  0  4  8</t>
+          <t>5  9  1  0</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>07/27(一)</t>
+          <t>07/28(二)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>5  9  1  0</t>
+          <t>0  4  3  3</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>07/28(二)</t>
+          <t>07/29(三)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>0  4  3  3</t>
+          <t>7  6  8  5</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>07/29(三)</t>
+          <t>07/30(四)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>7  6  8  5</t>
+          <t>2  9  3  1</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>07/30(四)</t>
+          <t>07/31(五)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2  9  3  1</t>
+          <t>7  1  9  8</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>07/31(五)</t>
+          <t>08/01(六)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>7  1  9  8</t>
+          <t>7  1  9  5</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>08/01(六)</t>
+          <t>08/03(一)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>7  1  9  5</t>
+          <t>6  0  1  6</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>08/03(一)</t>
+          <t>08/04(二)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>6  0  1  6</t>
+          <t>1  8  4  3</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/04(二)</t>
+          <t>08/05(三)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>1  8  4  3</t>
+          <t>0  8  2  3</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/05(三)</t>
+          <t>08/06(四)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>0  8  2  3</t>
+          <t>6  3  4  5</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>07/27(一)</t>
+          <t>07/28(二)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>6  0  2</t>
+          <t>7  1  6</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>07/28(二)</t>
+          <t>07/29(三)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>7  1  6</t>
+          <t>8  4  6</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>07/29(三)</t>
+          <t>07/30(四)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>8  4  6</t>
+          <t>2  8  5</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>07/30(四)</t>
+          <t>07/31(五)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2  8  5</t>
+          <t>1  3  9</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>07/31(五)</t>
+          <t>08/01(六)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>1  3  9</t>
+          <t>5  6  6</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>08/01(六)</t>
+          <t>08/03(一)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>5  6  6</t>
+          <t>4  9  1</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>08/03(一)</t>
+          <t>08/04(二)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>4  9  1</t>
+          <t>9  9  1</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>08/04(二)</t>
+          <t>08/05(三)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>9  9  1</t>
+          <t>3  1  5</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>08/05(三)</t>
+          <t>08/06(四)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>3  1  5</t>
+          <t>1  0  7</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>08/06(四)</t>
+          <t>08/07(五)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>1  0  7</t>
+          <t>9  6  9</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>07/27(一)</t>
+          <t>07/28(二)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>5  9  1  0</t>
+          <t>0  4  3  3</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>07/28(二)</t>
+          <t>07/29(三)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>0  4  3  3</t>
+          <t>7  6  8  5</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>07/29(三)</t>
+          <t>07/30(四)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>7  6  8  5</t>
+          <t>2  9  3  1</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>07/30(四)</t>
+          <t>07/31(五)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2  9  3  1</t>
+          <t>7  1  9  8</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>07/31(五)</t>
+          <t>08/01(六)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>7  1  9  8</t>
+          <t>7  1  9  5</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>08/01(六)</t>
+          <t>08/03(一)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>7  1  9  5</t>
+          <t>6  0  1  6</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>08/03(一)</t>
+          <t>08/04(二)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>6  0  1  6</t>
+          <t>1  8  4  3</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>08/04(二)</t>
+          <t>08/05(三)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>1  8  4  3</t>
+          <t>0  8  2  3</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/05(三)</t>
+          <t>08/06(四)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>0  8  2  3</t>
+          <t>6  3  4  5</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/06(四)</t>
+          <t>08/07(五)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>6  3  4  5</t>
+          <t>1  1  9  3</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000182</v>
+        <v>115000183</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.07.28</t>
+          <t>115.07.29</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>05  08  13  23  31</t>
+          <t>05  14  32  33  36</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000183</v>
+        <v>115000184</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.07.29</t>
+          <t>115.07.30</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>05  14  32  33  36</t>
+          <t>04  07  08  16  38</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000184</v>
+        <v>115000185</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.07.30</t>
+          <t>115.07.31</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>04  07  08  16  38</t>
+          <t>01  09  12  25  26</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000185</v>
+        <v>115000186</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.07.31</t>
+          <t>115.08.01</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>01  09  12  25  26</t>
+          <t>06  11  18  22  29</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000186</v>
+        <v>115000187</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.08.01</t>
+          <t>115.08.03</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>06  11  18  22  29</t>
+          <t>07  21  23  28  35</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000187</v>
+        <v>115000188</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.08.03</t>
+          <t>115.08.04</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>07  21  23  28  35</t>
+          <t>09  32  35  37  39</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000188</v>
+        <v>115000189</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.08.04</t>
+          <t>115.08.05</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>09  32  35  37  39</t>
+          <t>02  04  22  25  29</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000189</v>
+        <v>115000190</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.08.05</t>
+          <t>115.08.06</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>02  04  22  25  29</t>
+          <t>03  09  16  24  35</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000190</v>
+        <v>115000191</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.08.06</t>
+          <t>115.08.07</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>03  09  16  24  35</t>
+          <t>06  11  12  13  19</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000191</v>
+        <v>115000192</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.08.07</t>
+          <t>115.08.08</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>06  11  12  13  19</t>
+          <t>05  11  24  31  32</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>07/28(二)</t>
+          <t>07/29(三)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>7  1  6</t>
+          <t>8  4  6</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>07/29(三)</t>
+          <t>07/30(四)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>8  4  6</t>
+          <t>2  8  5</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>07/30(四)</t>
+          <t>07/31(五)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2  8  5</t>
+          <t>1  3  9</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>07/31(五)</t>
+          <t>08/01(六)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>1  3  9</t>
+          <t>5  6  6</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>08/01(六)</t>
+          <t>08/03(一)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>5  6  6</t>
+          <t>4  9  1</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>08/03(一)</t>
+          <t>08/04(二)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>4  9  1</t>
+          <t>9  9  1</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>08/04(二)</t>
+          <t>08/05(三)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>9  9  1</t>
+          <t>3  1  5</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>08/05(三)</t>
+          <t>08/06(四)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>3  1  5</t>
+          <t>1  0  7</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>08/06(四)</t>
+          <t>08/07(五)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>1  0  7</t>
+          <t>9  6  9</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>08/07(五)</t>
+          <t>08/08(六)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>9  6  9</t>
+          <t>2  1  9</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>07/28(二)</t>
+          <t>07/29(三)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>0  4  3  3</t>
+          <t>7  6  8  5</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>07/29(三)</t>
+          <t>07/30(四)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>7  6  8  5</t>
+          <t>2  9  3  1</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>07/30(四)</t>
+          <t>07/31(五)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2  9  3  1</t>
+          <t>7  1  9  8</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>07/31(五)</t>
+          <t>08/01(六)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>7  1  9  8</t>
+          <t>7  1  9  5</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>08/01(六)</t>
+          <t>08/03(一)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>7  1  9  5</t>
+          <t>6  0  1  6</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>08/03(一)</t>
+          <t>08/04(二)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>6  0  1  6</t>
+          <t>1  8  4  3</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>08/04(二)</t>
+          <t>08/05(三)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>1  8  4  3</t>
+          <t>0  8  2  3</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>08/05(三)</t>
+          <t>08/06(四)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>0  8  2  3</t>
+          <t>6  3  4  5</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/06(四)</t>
+          <t>08/07(五)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>6  3  4  5</t>
+          <t>1  1  9  3</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/07(五)</t>
+          <t>08/08(六)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>1  1  9  3</t>
+          <t>9  6  2  4</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000183</v>
+        <v>115000184</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.07.29</t>
+          <t>115.07.30</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>05  14  32  33  36</t>
+          <t>04  07  08  16  38</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000184</v>
+        <v>115000185</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.07.30</t>
+          <t>115.07.31</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>04  07  08  16  38</t>
+          <t>01  09  12  25  26</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000185</v>
+        <v>115000186</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.07.31</t>
+          <t>115.08.01</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>01  09  12  25  26</t>
+          <t>06  11  18  22  29</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000186</v>
+        <v>115000187</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.08.01</t>
+          <t>115.08.03</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>06  11  18  22  29</t>
+          <t>07  21  23  28  35</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000187</v>
+        <v>115000188</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.08.03</t>
+          <t>115.08.04</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>07  21  23  28  35</t>
+          <t>09  32  35  37  39</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000188</v>
+        <v>115000189</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.08.04</t>
+          <t>115.08.05</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>09  32  35  37  39</t>
+          <t>02  04  22  25  29</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000189</v>
+        <v>115000190</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.08.05</t>
+          <t>115.08.06</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>02  04  22  25  29</t>
+          <t>03  09  16  24  35</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000190</v>
+        <v>115000191</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.08.06</t>
+          <t>115.08.07</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>03  09  16  24  35</t>
+          <t>06  11  12  13  19</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000191</v>
+        <v>115000192</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.08.07</t>
+          <t>115.08.08</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>06  11  12  13  19</t>
+          <t>05  11  24  31  32</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000192</v>
+        <v>115000193</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.08.08</t>
+          <t>115.08.10</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>05  11  24  31  32</t>
+          <t>01  07  16  23  35</t>
         </is>
       </c>
     </row>
@@ -1354,36 +1354,36 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000054</v>
+        <v>115000055</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.07.06</t>
+          <t>115.07.09</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>04  12  15  24  30  31</t>
+          <t>10  22  24  29  35  37</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000055</v>
+        <v>115000056</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.07.09</t>
+          <t>115.07.13</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>10  22  24  29  35  37</t>
+          <t>11  24  29  32  35  38</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -1394,76 +1394,76 @@
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.07.13</t>
+          <t>115.07.16</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>11  24  29  32  35  38</t>
+          <t>17  23  25  29  34  36</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.07.16</t>
+          <t>115.07.20</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>17  23  25  29  34  36</t>
+          <t>06  12  13  23  29  31</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.07.20</t>
+          <t>115.07.23</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>06  12  13  23  29  31</t>
+          <t>08  10  13  21  29  31</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.07.23</t>
+          <t>115.07.27</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>08  10  13  21  29  31</t>
+          <t>19  22  28  31  33  35</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -1474,16 +1474,16 @@
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.07.27</t>
+          <t>115.07.30</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>19  22  28  31  33  35</t>
+          <t>08  14  17  19  21  23</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -1494,16 +1494,16 @@
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.07.30</t>
+          <t>115.08.03</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>08  14  17  19  21  23</t>
+          <t>04  15  22  26  34  36</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -1514,41 +1514,41 @@
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.08.03</t>
+          <t>115.08.06</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>04  15  22  26  34  36</t>
+          <t>02  07  08  20  26  33</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>04</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.08.06</t>
+          <t>115.08.10</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>02  07  08  20  26  33</t>
+          <t>11  25  28  30  31  36</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>07/29(三)</t>
+          <t>07/30(四)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>8  4  6</t>
+          <t>2  8  5</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>07/30(四)</t>
+          <t>07/31(五)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2  8  5</t>
+          <t>1  3  9</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>07/31(五)</t>
+          <t>08/01(六)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>1  3  9</t>
+          <t>5  6  6</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>08/01(六)</t>
+          <t>08/03(一)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>5  6  6</t>
+          <t>4  9  1</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>08/03(一)</t>
+          <t>08/04(二)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>4  9  1</t>
+          <t>9  9  1</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>08/04(二)</t>
+          <t>08/05(三)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>9  9  1</t>
+          <t>3  1  5</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>08/05(三)</t>
+          <t>08/06(四)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>3  1  5</t>
+          <t>1  0  7</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>08/06(四)</t>
+          <t>08/07(五)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>1  0  7</t>
+          <t>9  6  9</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>08/07(五)</t>
+          <t>08/08(六)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>9  6  9</t>
+          <t>2  1  9</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>08/08(六)</t>
+          <t>08/10(一)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>2  1  9</t>
+          <t>1  2  4</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>07/29(三)</t>
+          <t>07/30(四)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>7  6  8  5</t>
+          <t>2  9  3  1</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>07/30(四)</t>
+          <t>07/31(五)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2  9  3  1</t>
+          <t>7  1  9  8</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>07/31(五)</t>
+          <t>08/01(六)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>7  1  9  8</t>
+          <t>7  1  9  5</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>08/01(六)</t>
+          <t>08/03(一)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>7  1  9  5</t>
+          <t>6  0  1  6</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>08/03(一)</t>
+          <t>08/04(二)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>6  0  1  6</t>
+          <t>1  8  4  3</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>08/04(二)</t>
+          <t>08/05(三)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>1  8  4  3</t>
+          <t>0  8  2  3</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>08/05(三)</t>
+          <t>08/06(四)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>0  8  2  3</t>
+          <t>6  3  4  5</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>08/06(四)</t>
+          <t>08/07(五)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>6  3  4  5</t>
+          <t>1  1  9  3</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/07(五)</t>
+          <t>08/08(六)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>1  1  9  3</t>
+          <t>9  6  2  4</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/08(六)</t>
+          <t>08/10(一)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>9  6  2  4</t>
+          <t>3  3  7  5</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000184</v>
+        <v>115000185</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.07.30</t>
+          <t>115.07.31</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>04  07  08  16  38</t>
+          <t>01  09  12  25  26</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000185</v>
+        <v>115000186</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.07.31</t>
+          <t>115.08.01</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>01  09  12  25  26</t>
+          <t>06  11  18  22  29</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000186</v>
+        <v>115000187</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.08.01</t>
+          <t>115.08.03</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>06  11  18  22  29</t>
+          <t>07  21  23  28  35</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000187</v>
+        <v>115000188</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.08.03</t>
+          <t>115.08.04</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>07  21  23  28  35</t>
+          <t>09  32  35  37  39</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000188</v>
+        <v>115000189</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.08.04</t>
+          <t>115.08.05</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>09  32  35  37  39</t>
+          <t>02  04  22  25  29</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000189</v>
+        <v>115000190</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.08.05</t>
+          <t>115.08.06</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>02  04  22  25  29</t>
+          <t>03  09  16  24  35</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000190</v>
+        <v>115000191</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.08.06</t>
+          <t>115.08.07</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>03  09  16  24  35</t>
+          <t>06  11  12  13  19</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000191</v>
+        <v>115000192</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.08.07</t>
+          <t>115.08.08</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>06  11  12  13  19</t>
+          <t>05  11  24  31  32</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000192</v>
+        <v>115000193</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.08.08</t>
+          <t>115.08.10</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>05  11  24  31  32</t>
+          <t>01  07  16  23  35</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000193</v>
+        <v>115000194</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.08.10</t>
+          <t>115.08.11</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>01  07  16  23  35</t>
+          <t>07  17  19  23  30</t>
         </is>
       </c>
     </row>
@@ -1789,201 +1789,201 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000068</v>
+        <v>115000069</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.07.07</t>
+          <t>115.07.10</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>08  13  15  18  19  42</t>
+          <t>03  04  15  18  29  49</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>13</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000069</v>
+        <v>115000070</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.07.10</t>
+          <t>115.07.14</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>03  04  15  18  29  49</t>
+          <t>10  25  34  36  45  46</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000070</v>
+        <v>115000071</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.07.14</t>
+          <t>115.07.17</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>10  25  34  36  45  46</t>
+          <t>01  06  12  14  17  26</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000071</v>
+        <v>115000072</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.07.17</t>
+          <t>115.07.21</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>01  06  12  14  17  26</t>
+          <t>02  08  15  26  35  46</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000072</v>
+        <v>115000073</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.07.21</t>
+          <t>115.07.24</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>02  08  15  26  35  46</t>
+          <t>03  15  27  34  35  44</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000073</v>
+        <v>115000074</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.07.24</t>
+          <t>115.07.28</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>03  15  27  34  35  44</t>
+          <t>08  19  24  26  32  43</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>47</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000074</v>
+        <v>115000075</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.07.28</t>
+          <t>115.07.31</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>08  19  24  26  32  43</t>
+          <t>11  20  23  33  34  44</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000075</v>
+        <v>115000076</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.07.31</t>
+          <t>115.08.04</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>11  20  23  33  34  44</t>
+          <t>04  09  15  30  36  49</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000076</v>
+        <v>115000077</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.08.04</t>
+          <t>115.08.07</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>04  09  15  30  36  49</t>
+          <t>02  12  19  21  25  41</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>31</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000077</v>
+        <v>115000078</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.08.07</t>
+          <t>115.08.11</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>02  12  19  21  25  41</t>
+          <t>08  12  16  24  29  46</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>07/30(四)</t>
+          <t>07/31(五)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>2  8  5</t>
+          <t>1  3  9</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>07/31(五)</t>
+          <t>08/01(六)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>1  3  9</t>
+          <t>5  6  6</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>08/01(六)</t>
+          <t>08/03(一)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>5  6  6</t>
+          <t>4  9  1</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>08/03(一)</t>
+          <t>08/04(二)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>4  9  1</t>
+          <t>9  9  1</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>08/04(二)</t>
+          <t>08/05(三)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>9  9  1</t>
+          <t>3  1  5</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>08/05(三)</t>
+          <t>08/06(四)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>3  1  5</t>
+          <t>1  0  7</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>08/06(四)</t>
+          <t>08/07(五)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>1  0  7</t>
+          <t>9  6  9</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>08/07(五)</t>
+          <t>08/08(六)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>9  6  9</t>
+          <t>2  1  9</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>08/08(六)</t>
+          <t>08/10(一)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>2  1  9</t>
+          <t>1  2  4</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>08/10(一)</t>
+          <t>08/11(二)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>1  2  4</t>
+          <t>6  2  3</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>07/30(四)</t>
+          <t>07/31(五)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2  9  3  1</t>
+          <t>7  1  9  8</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>07/31(五)</t>
+          <t>08/01(六)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>7  1  9  8</t>
+          <t>7  1  9  5</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>08/01(六)</t>
+          <t>08/03(一)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>7  1  9  5</t>
+          <t>6  0  1  6</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>08/03(一)</t>
+          <t>08/04(二)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>6  0  1  6</t>
+          <t>1  8  4  3</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>08/04(二)</t>
+          <t>08/05(三)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>1  8  4  3</t>
+          <t>0  8  2  3</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>08/05(三)</t>
+          <t>08/06(四)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>0  8  2  3</t>
+          <t>6  3  4  5</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>08/06(四)</t>
+          <t>08/07(五)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>6  3  4  5</t>
+          <t>1  1  9  3</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>08/07(五)</t>
+          <t>08/08(六)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>1  1  9  3</t>
+          <t>9  6  2  4</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/08(六)</t>
+          <t>08/10(一)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>9  6  2  4</t>
+          <t>3  3  7  5</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/10(一)</t>
+          <t>08/11(二)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>3  3  7  5</t>
+          <t>0  2  3  4</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000185</v>
+        <v>115000186</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.07.31</t>
+          <t>115.08.01</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>01  09  12  25  26</t>
+          <t>06  11  18  22  29</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000186</v>
+        <v>115000187</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.08.01</t>
+          <t>115.08.03</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>06  11  18  22  29</t>
+          <t>07  21  23  28  35</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000187</v>
+        <v>115000188</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.08.03</t>
+          <t>115.08.04</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>07  21  23  28  35</t>
+          <t>09  32  35  37  39</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000188</v>
+        <v>115000189</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.08.04</t>
+          <t>115.08.05</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>09  32  35  37  39</t>
+          <t>02  04  22  25  29</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000189</v>
+        <v>115000190</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.08.05</t>
+          <t>115.08.06</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>02  04  22  25  29</t>
+          <t>03  09  16  24  35</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000190</v>
+        <v>115000191</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.08.06</t>
+          <t>115.08.07</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>03  09  16  24  35</t>
+          <t>06  11  12  13  19</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000191</v>
+        <v>115000192</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.08.07</t>
+          <t>115.08.08</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>06  11  12  13  19</t>
+          <t>05  11  24  31  32</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000192</v>
+        <v>115000193</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.08.08</t>
+          <t>115.08.10</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>05  11  24  31  32</t>
+          <t>01  07  16  23  35</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000193</v>
+        <v>115000194</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.08.10</t>
+          <t>115.08.11</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>01  07  16  23  35</t>
+          <t>07  17  19  23  30</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000194</v>
+        <v>115000195</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.08.11</t>
+          <t>115.08.12</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>07  17  19  23  30</t>
+          <t>07  12  17  20  32</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>07/31(五)</t>
+          <t>08/01(六)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>1  3  9</t>
+          <t>5  6  6</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>08/01(六)</t>
+          <t>08/03(一)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>5  6  6</t>
+          <t>4  9  1</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>08/03(一)</t>
+          <t>08/04(二)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>4  9  1</t>
+          <t>9  9  1</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>08/04(二)</t>
+          <t>08/05(三)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>9  9  1</t>
+          <t>3  1  5</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>08/05(三)</t>
+          <t>08/06(四)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>3  1  5</t>
+          <t>1  0  7</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>08/06(四)</t>
+          <t>08/07(五)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>1  0  7</t>
+          <t>9  6  9</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>08/07(五)</t>
+          <t>08/08(六)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>9  6  9</t>
+          <t>2  1  9</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>08/08(六)</t>
+          <t>08/10(一)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2  1  9</t>
+          <t>1  2  4</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>08/10(一)</t>
+          <t>08/11(二)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>1  2  4</t>
+          <t>6  2  3</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>08/11(二)</t>
+          <t>08/12(三)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>6  2  3</t>
+          <t>9  1  0</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>07/31(五)</t>
+          <t>08/01(六)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>7  1  9  8</t>
+          <t>7  1  9  5</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>08/01(六)</t>
+          <t>08/03(一)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>7  1  9  5</t>
+          <t>6  0  1  6</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>08/03(一)</t>
+          <t>08/04(二)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>6  0  1  6</t>
+          <t>1  8  4  3</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>08/04(二)</t>
+          <t>08/05(三)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>1  8  4  3</t>
+          <t>0  8  2  3</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>08/05(三)</t>
+          <t>08/06(四)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>0  8  2  3</t>
+          <t>6  3  4  5</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>08/06(四)</t>
+          <t>08/07(五)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>6  3  4  5</t>
+          <t>1  1  9  3</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>08/07(五)</t>
+          <t>08/08(六)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>1  1  9  3</t>
+          <t>9  6  2  4</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>08/08(六)</t>
+          <t>08/10(一)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>9  6  2  4</t>
+          <t>3  3  7  5</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/10(一)</t>
+          <t>08/11(二)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>3  3  7  5</t>
+          <t>0  2  3  4</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/11(二)</t>
+          <t>08/12(三)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>0  2  3  4</t>
+          <t>9  1  3  1</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000186</v>
+        <v>115000187</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.08.01</t>
+          <t>115.08.03</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>06  11  18  22  29</t>
+          <t>07  21  23  28  35</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000187</v>
+        <v>115000188</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.08.03</t>
+          <t>115.08.04</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>07  21  23  28  35</t>
+          <t>09  32  35  37  39</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000188</v>
+        <v>115000189</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.08.04</t>
+          <t>115.08.05</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>09  32  35  37  39</t>
+          <t>02  04  22  25  29</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000189</v>
+        <v>115000190</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.08.05</t>
+          <t>115.08.06</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>02  04  22  25  29</t>
+          <t>03  09  16  24  35</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000190</v>
+        <v>115000191</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.08.06</t>
+          <t>115.08.07</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>03  09  16  24  35</t>
+          <t>06  11  12  13  19</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000191</v>
+        <v>115000192</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.08.07</t>
+          <t>115.08.08</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>06  11  12  13  19</t>
+          <t>05  11  24  31  32</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000192</v>
+        <v>115000193</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.08.08</t>
+          <t>115.08.10</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>05  11  24  31  32</t>
+          <t>01  07  16  23  35</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000193</v>
+        <v>115000194</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.08.10</t>
+          <t>115.08.11</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>01  07  16  23  35</t>
+          <t>07  17  19  23  30</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000194</v>
+        <v>115000195</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.08.11</t>
+          <t>115.08.12</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>07  17  19  23  30</t>
+          <t>07  12  17  20  32</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000195</v>
+        <v>115000196</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.08.12</t>
+          <t>115.08.13</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>07  12  17  20  32</t>
+          <t>05  11  12  17  18</t>
         </is>
       </c>
     </row>
@@ -1354,16 +1354,16 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000055</v>
+        <v>115000056</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.07.09</t>
+          <t>115.07.13</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>10  22  24  29  35  37</t>
+          <t>11  24  29  32  35  38</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
@@ -1374,76 +1374,76 @@
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.07.13</t>
+          <t>115.07.16</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>11  24  29  32  35  38</t>
+          <t>17  23  25  29  34  36</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.07.16</t>
+          <t>115.07.20</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>17  23  25  29  34  36</t>
+          <t>06  12  13  23  29  31</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.07.20</t>
+          <t>115.07.23</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>06  12  13  23  29  31</t>
+          <t>08  10  13  21  29  31</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.07.23</t>
+          <t>115.07.27</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>08  10  13  21  29  31</t>
+          <t>19  22  28  31  33  35</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -1454,16 +1454,16 @@
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.07.27</t>
+          <t>115.07.30</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>19  22  28  31  33  35</t>
+          <t>08  14  17  19  21  23</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -1474,16 +1474,16 @@
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.07.30</t>
+          <t>115.08.03</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>08  14  17  19  21  23</t>
+          <t>04  15  22  26  34  36</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -1494,61 +1494,61 @@
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.08.03</t>
+          <t>115.08.06</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>04  15  22  26  34  36</t>
+          <t>02  07  08  20  26  33</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>04</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.08.06</t>
+          <t>115.08.10</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>02  07  08  20  26  33</t>
+          <t>11  25  28  30  31  36</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.08.10</t>
+          <t>115.08.13</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>11  25  28  30  31  36</t>
+          <t>01  03  04  07  10  19</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>06</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>08/01(六)</t>
+          <t>08/03(一)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>5  6  6</t>
+          <t>4  9  1</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>08/03(一)</t>
+          <t>08/04(二)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>4  9  1</t>
+          <t>9  9  1</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>08/04(二)</t>
+          <t>08/05(三)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>9  9  1</t>
+          <t>3  1  5</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>08/05(三)</t>
+          <t>08/06(四)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>3  1  5</t>
+          <t>1  0  7</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>08/06(四)</t>
+          <t>08/07(五)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>1  0  7</t>
+          <t>9  6  9</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>08/07(五)</t>
+          <t>08/08(六)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>9  6  9</t>
+          <t>2  1  9</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>08/08(六)</t>
+          <t>08/10(一)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>2  1  9</t>
+          <t>1  2  4</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>08/10(一)</t>
+          <t>08/11(二)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>1  2  4</t>
+          <t>6  2  3</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>08/11(二)</t>
+          <t>08/12(三)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>6  2  3</t>
+          <t>9  1  0</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>08/12(三)</t>
+          <t>08/13(四)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>9  1  0</t>
+          <t>2  5  7</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>08/01(六)</t>
+          <t>08/03(一)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>7  1  9  5</t>
+          <t>6  0  1  6</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>08/03(一)</t>
+          <t>08/04(二)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>6  0  1  6</t>
+          <t>1  8  4  3</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>08/04(二)</t>
+          <t>08/05(三)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>1  8  4  3</t>
+          <t>0  8  2  3</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>08/05(三)</t>
+          <t>08/06(四)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>0  8  2  3</t>
+          <t>6  3  4  5</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>08/06(四)</t>
+          <t>08/07(五)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>6  3  4  5</t>
+          <t>1  1  9  3</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>08/07(五)</t>
+          <t>08/08(六)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>1  1  9  3</t>
+          <t>9  6  2  4</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>08/08(六)</t>
+          <t>08/10(一)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>9  6  2  4</t>
+          <t>3  3  7  5</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>08/10(一)</t>
+          <t>08/11(二)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>3  3  7  5</t>
+          <t>0  2  3  4</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/11(二)</t>
+          <t>08/12(三)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>0  2  3  4</t>
+          <t>9  1  3  1</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/12(三)</t>
+          <t>08/13(四)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>9  1  3  1</t>
+          <t>5  7  7  0</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000187</v>
+        <v>115000188</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.08.03</t>
+          <t>115.08.04</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>07  21  23  28  35</t>
+          <t>09  32  35  37  39</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000188</v>
+        <v>115000189</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.08.04</t>
+          <t>115.08.05</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>09  32  35  37  39</t>
+          <t>02  04  22  25  29</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000189</v>
+        <v>115000190</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.08.05</t>
+          <t>115.08.06</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>02  04  22  25  29</t>
+          <t>03  09  16  24  35</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000190</v>
+        <v>115000191</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.08.06</t>
+          <t>115.08.07</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>03  09  16  24  35</t>
+          <t>06  11  12  13  19</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000191</v>
+        <v>115000192</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.08.07</t>
+          <t>115.08.08</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>06  11  12  13  19</t>
+          <t>05  11  24  31  32</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000192</v>
+        <v>115000193</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.08.08</t>
+          <t>115.08.10</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>05  11  24  31  32</t>
+          <t>01  07  16  23  35</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000193</v>
+        <v>115000194</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.08.10</t>
+          <t>115.08.11</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>01  07  16  23  35</t>
+          <t>07  17  19  23  30</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000194</v>
+        <v>115000195</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.08.11</t>
+          <t>115.08.12</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>07  17  19  23  30</t>
+          <t>07  12  17  20  32</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000195</v>
+        <v>115000196</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.08.12</t>
+          <t>115.08.13</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>07  12  17  20  32</t>
+          <t>05  11  12  17  18</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000196</v>
+        <v>115000197</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.08.13</t>
+          <t>115.08.14</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>05  11  12  17  18</t>
+          <t>07  19  21  25  34</t>
         </is>
       </c>
     </row>
@@ -1789,201 +1789,201 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000069</v>
+        <v>115000070</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.07.10</t>
+          <t>115.07.14</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>03  04  15  18  29  49</t>
+          <t>10  25  34  36  45  46</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000070</v>
+        <v>115000071</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.07.14</t>
+          <t>115.07.17</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>10  25  34  36  45  46</t>
+          <t>01  06  12  14  17  26</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000071</v>
+        <v>115000072</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.07.17</t>
+          <t>115.07.21</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>01  06  12  14  17  26</t>
+          <t>02  08  15  26  35  46</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000072</v>
+        <v>115000073</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.07.21</t>
+          <t>115.07.24</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>02  08  15  26  35  46</t>
+          <t>03  15  27  34  35  44</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000073</v>
+        <v>115000074</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.07.24</t>
+          <t>115.07.28</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>03  15  27  34  35  44</t>
+          <t>08  19  24  26  32  43</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>47</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000074</v>
+        <v>115000075</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.07.28</t>
+          <t>115.07.31</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>08  19  24  26  32  43</t>
+          <t>11  20  23  33  34  44</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000075</v>
+        <v>115000076</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.07.31</t>
+          <t>115.08.04</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>11  20  23  33  34  44</t>
+          <t>04  09  15  30  36  49</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000076</v>
+        <v>115000077</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.08.04</t>
+          <t>115.08.07</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>04  09  15  30  36  49</t>
+          <t>02  12  19  21  25  41</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>31</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000077</v>
+        <v>115000078</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.08.07</t>
+          <t>115.08.11</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>02  12  19  21  25  41</t>
+          <t>08  12  16  24  29  46</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000078</v>
+        <v>115000079</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.08.11</t>
+          <t>115.08.14</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>08  12  16  24  29  46</t>
+          <t>05  12  25  33  34  35</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>08/03(一)</t>
+          <t>08/04(二)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>4  9  1</t>
+          <t>9  9  1</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>08/04(二)</t>
+          <t>08/05(三)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>9  9  1</t>
+          <t>3  1  5</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>08/05(三)</t>
+          <t>08/06(四)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>3  1  5</t>
+          <t>1  0  7</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>08/06(四)</t>
+          <t>08/07(五)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>1  0  7</t>
+          <t>9  6  9</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>08/07(五)</t>
+          <t>08/08(六)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>9  6  9</t>
+          <t>2  1  9</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>08/08(六)</t>
+          <t>08/10(一)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2  1  9</t>
+          <t>1  2  4</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>08/10(一)</t>
+          <t>08/11(二)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>1  2  4</t>
+          <t>6  2  3</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>08/11(二)</t>
+          <t>08/12(三)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>6  2  3</t>
+          <t>9  1  0</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>08/12(三)</t>
+          <t>08/13(四)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>9  1  0</t>
+          <t>2  5  7</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>08/13(四)</t>
+          <t>08/14(五)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>2  5  7</t>
+          <t>1  7  7</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>08/03(一)</t>
+          <t>08/04(二)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>6  0  1  6</t>
+          <t>1  8  4  3</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>08/04(二)</t>
+          <t>08/05(三)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>1  8  4  3</t>
+          <t>0  8  2  3</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>08/05(三)</t>
+          <t>08/06(四)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>0  8  2  3</t>
+          <t>6  3  4  5</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>08/06(四)</t>
+          <t>08/07(五)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>6  3  4  5</t>
+          <t>1  1  9  3</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>08/07(五)</t>
+          <t>08/08(六)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>1  1  9  3</t>
+          <t>9  6  2  4</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>08/08(六)</t>
+          <t>08/10(一)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>9  6  2  4</t>
+          <t>3  3  7  5</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>08/10(一)</t>
+          <t>08/11(二)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>3  3  7  5</t>
+          <t>0  2  3  4</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>08/11(二)</t>
+          <t>08/12(三)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>0  2  3  4</t>
+          <t>9  1  3  1</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/12(三)</t>
+          <t>08/13(四)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>9  1  3  1</t>
+          <t>5  7  7  0</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/13(四)</t>
+          <t>08/14(五)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>5  7  7  0</t>
+          <t>5  4  1  5</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000188</v>
+        <v>115000189</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.08.04</t>
+          <t>115.08.05</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>09  32  35  37  39</t>
+          <t>02  04  22  25  29</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000189</v>
+        <v>115000190</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.08.05</t>
+          <t>115.08.06</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>02  04  22  25  29</t>
+          <t>03  09  16  24  35</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000190</v>
+        <v>115000191</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.08.06</t>
+          <t>115.08.07</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>03  09  16  24  35</t>
+          <t>06  11  12  13  19</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000191</v>
+        <v>115000192</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.08.07</t>
+          <t>115.08.08</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>06  11  12  13  19</t>
+          <t>05  11  24  31  32</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000192</v>
+        <v>115000193</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.08.08</t>
+          <t>115.08.10</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>05  11  24  31  32</t>
+          <t>01  07  16  23  35</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000193</v>
+        <v>115000194</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.08.10</t>
+          <t>115.08.11</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>01  07  16  23  35</t>
+          <t>07  17  19  23  30</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000194</v>
+        <v>115000195</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.08.11</t>
+          <t>115.08.12</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>07  17  19  23  30</t>
+          <t>07  12  17  20  32</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000195</v>
+        <v>115000196</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.08.12</t>
+          <t>115.08.13</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>07  12  17  20  32</t>
+          <t>05  11  12  17  18</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000196</v>
+        <v>115000197</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.08.13</t>
+          <t>115.08.14</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>05  11  12  17  18</t>
+          <t>07  19  21  25  34</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000197</v>
+        <v>115000198</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.08.14</t>
+          <t>115.08.15</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>07  19  21  25  34</t>
+          <t>12  14  21  35  37</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>08/04(二)</t>
+          <t>08/05(三)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>9  9  1</t>
+          <t>3  1  5</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>08/05(三)</t>
+          <t>08/06(四)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>3  1  5</t>
+          <t>1  0  7</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>08/06(四)</t>
+          <t>08/07(五)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>1  0  7</t>
+          <t>9  6  9</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>08/07(五)</t>
+          <t>08/08(六)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>9  6  9</t>
+          <t>2  1  9</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>08/08(六)</t>
+          <t>08/10(一)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2  1  9</t>
+          <t>1  2  4</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>08/10(一)</t>
+          <t>08/11(二)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>1  2  4</t>
+          <t>6  2  3</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>08/11(二)</t>
+          <t>08/12(三)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>6  2  3</t>
+          <t>9  1  0</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>08/12(三)</t>
+          <t>08/13(四)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>9  1  0</t>
+          <t>2  5  7</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>08/13(四)</t>
+          <t>08/14(五)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>2  5  7</t>
+          <t>1  7  7</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>08/14(五)</t>
+          <t>08/15(六)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>1  7  7</t>
+          <t>1  9  5</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>08/04(二)</t>
+          <t>08/05(三)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>1  8  4  3</t>
+          <t>0  8  2  3</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>08/05(三)</t>
+          <t>08/06(四)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>0  8  2  3</t>
+          <t>6  3  4  5</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>08/06(四)</t>
+          <t>08/07(五)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>6  3  4  5</t>
+          <t>1  1  9  3</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>08/07(五)</t>
+          <t>08/08(六)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>1  1  9  3</t>
+          <t>9  6  2  4</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>08/08(六)</t>
+          <t>08/10(一)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>9  6  2  4</t>
+          <t>3  3  7  5</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>08/10(一)</t>
+          <t>08/11(二)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>3  3  7  5</t>
+          <t>0  2  3  4</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>08/11(二)</t>
+          <t>08/12(三)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>0  2  3  4</t>
+          <t>9  1  3  1</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>08/12(三)</t>
+          <t>08/13(四)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>9  1  3  1</t>
+          <t>5  7  7  0</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/13(四)</t>
+          <t>08/14(五)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>5  7  7  0</t>
+          <t>5  4  1  5</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/14(五)</t>
+          <t>08/15(六)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>5  4  1  5</t>
+          <t>2  3  9  5</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000189</v>
+        <v>115000190</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.08.05</t>
+          <t>115.08.06</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>02  04  22  25  29</t>
+          <t>03  09  16  24  35</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000190</v>
+        <v>115000191</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.08.06</t>
+          <t>115.08.07</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>03  09  16  24  35</t>
+          <t>06  11  12  13  19</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000191</v>
+        <v>115000192</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.08.07</t>
+          <t>115.08.08</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>06  11  12  13  19</t>
+          <t>05  11  24  31  32</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000192</v>
+        <v>115000193</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.08.08</t>
+          <t>115.08.10</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>05  11  24  31  32</t>
+          <t>01  07  16  23  35</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000193</v>
+        <v>115000194</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.08.10</t>
+          <t>115.08.11</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>01  07  16  23  35</t>
+          <t>07  17  19  23  30</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000194</v>
+        <v>115000195</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.08.11</t>
+          <t>115.08.12</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>07  17  19  23  30</t>
+          <t>07  12  17  20  32</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000195</v>
+        <v>115000196</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.08.12</t>
+          <t>115.08.13</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>07  12  17  20  32</t>
+          <t>05  11  12  17  18</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000196</v>
+        <v>115000197</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.08.13</t>
+          <t>115.08.14</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>05  11  12  17  18</t>
+          <t>07  19  21  25  34</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000197</v>
+        <v>115000198</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.08.14</t>
+          <t>115.08.15</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>07  19  21  25  34</t>
+          <t>12  14  21  35  37</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000198</v>
+        <v>115000199</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.08.15</t>
+          <t>115.08.17</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>12  14  21  35  37</t>
+          <t>19  22  27  28  38</t>
         </is>
       </c>
     </row>
@@ -1354,76 +1354,76 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.07.13</t>
+          <t>115.07.16</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>11  24  29  32  35  38</t>
+          <t>17  23  25  29  34  36</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.07.16</t>
+          <t>115.07.20</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>17  23  25  29  34  36</t>
+          <t>06  12  13  23  29  31</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.07.20</t>
+          <t>115.07.23</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>06  12  13  23  29  31</t>
+          <t>08  10  13  21  29  31</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.07.23</t>
+          <t>115.07.27</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>08  10  13  21  29  31</t>
+          <t>19  22  28  31  33  35</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -1434,16 +1434,16 @@
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.07.27</t>
+          <t>115.07.30</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>19  22  28  31  33  35</t>
+          <t>08  14  17  19  21  23</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -1454,16 +1454,16 @@
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.07.30</t>
+          <t>115.08.03</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>08  14  17  19  21  23</t>
+          <t>04  15  22  26  34  36</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -1474,81 +1474,81 @@
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.08.03</t>
+          <t>115.08.06</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>04  15  22  26  34  36</t>
+          <t>02  07  08  20  26  33</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>04</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.08.06</t>
+          <t>115.08.10</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>02  07  08  20  26  33</t>
+          <t>11  25  28  30  31  36</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.08.10</t>
+          <t>115.08.13</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>11  25  28  30  31  36</t>
+          <t>01  03  04  07  10  19</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.08.13</t>
+          <t>115.08.17</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>01  03  04  07  10  19</t>
+          <t>05  11  18  19  35  38</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>08</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>08/05(三)</t>
+          <t>08/06(四)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>3  1  5</t>
+          <t>1  0  7</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>08/06(四)</t>
+          <t>08/07(五)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>1  0  7</t>
+          <t>9  6  9</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>08/07(五)</t>
+          <t>08/08(六)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>9  6  9</t>
+          <t>2  1  9</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>08/08(六)</t>
+          <t>08/10(一)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2  1  9</t>
+          <t>1  2  4</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>08/10(一)</t>
+          <t>08/11(二)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>1  2  4</t>
+          <t>6  2  3</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>08/11(二)</t>
+          <t>08/12(三)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>6  2  3</t>
+          <t>9  1  0</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>08/12(三)</t>
+          <t>08/13(四)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>9  1  0</t>
+          <t>2  5  7</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>08/13(四)</t>
+          <t>08/14(五)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2  5  7</t>
+          <t>1  7  7</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>08/14(五)</t>
+          <t>08/15(六)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>1  7  7</t>
+          <t>1  9  5</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>08/15(六)</t>
+          <t>08/17(一)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>1  9  5</t>
+          <t>3  5  4</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>08/05(三)</t>
+          <t>08/06(四)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>0  8  2  3</t>
+          <t>6  3  4  5</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>08/06(四)</t>
+          <t>08/07(五)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>6  3  4  5</t>
+          <t>1  1  9  3</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>08/07(五)</t>
+          <t>08/08(六)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>1  1  9  3</t>
+          <t>9  6  2  4</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>08/08(六)</t>
+          <t>08/10(一)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>9  6  2  4</t>
+          <t>3  3  7  5</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>08/10(一)</t>
+          <t>08/11(二)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>3  3  7  5</t>
+          <t>0  2  3  4</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>08/11(二)</t>
+          <t>08/12(三)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>0  2  3  4</t>
+          <t>9  1  3  1</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>08/12(三)</t>
+          <t>08/13(四)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>9  1  3  1</t>
+          <t>5  7  7  0</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>08/13(四)</t>
+          <t>08/14(五)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>5  7  7  0</t>
+          <t>5  4  1  5</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/14(五)</t>
+          <t>08/15(六)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>5  4  1  5</t>
+          <t>2  3  9  5</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/15(六)</t>
+          <t>08/17(一)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>2  3  9  5</t>
+          <t>6  7  5  3</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000190</v>
+        <v>115000191</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.08.06</t>
+          <t>115.08.07</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>03  09  16  24  35</t>
+          <t>06  11  12  13  19</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000191</v>
+        <v>115000192</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.08.07</t>
+          <t>115.08.08</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>06  11  12  13  19</t>
+          <t>05  11  24  31  32</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000192</v>
+        <v>115000193</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.08.08</t>
+          <t>115.08.10</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>05  11  24  31  32</t>
+          <t>01  07  16  23  35</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000193</v>
+        <v>115000194</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.08.10</t>
+          <t>115.08.11</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>01  07  16  23  35</t>
+          <t>07  17  19  23  30</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000194</v>
+        <v>115000195</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.08.11</t>
+          <t>115.08.12</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>07  17  19  23  30</t>
+          <t>07  12  17  20  32</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000195</v>
+        <v>115000196</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.08.12</t>
+          <t>115.08.13</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>07  12  17  20  32</t>
+          <t>05  11  12  17  18</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000196</v>
+        <v>115000197</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.08.13</t>
+          <t>115.08.14</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>05  11  12  17  18</t>
+          <t>07  19  21  25  34</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000197</v>
+        <v>115000198</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.08.14</t>
+          <t>115.08.15</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>07  19  21  25  34</t>
+          <t>12  14  21  35  37</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000198</v>
+        <v>115000199</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.08.15</t>
+          <t>115.08.17</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>12  14  21  35  37</t>
+          <t>19  22  27  28  38</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000199</v>
+        <v>115000200</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.08.17</t>
+          <t>115.08.18</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>19  22  27  28  38</t>
+          <t>05  06  10  28  39</t>
         </is>
       </c>
     </row>
@@ -1789,201 +1789,201 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000070</v>
+        <v>115000071</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.07.14</t>
+          <t>115.07.17</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>10  25  34  36  45  46</t>
+          <t>01  06  12  14  17  26</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000071</v>
+        <v>115000072</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.07.17</t>
+          <t>115.07.21</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>01  06  12  14  17  26</t>
+          <t>02  08  15  26  35  46</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000072</v>
+        <v>115000073</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.07.21</t>
+          <t>115.07.24</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>02  08  15  26  35  46</t>
+          <t>03  15  27  34  35  44</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000073</v>
+        <v>115000074</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.07.24</t>
+          <t>115.07.28</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>03  15  27  34  35  44</t>
+          <t>08  19  24  26  32  43</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>47</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000074</v>
+        <v>115000075</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.07.28</t>
+          <t>115.07.31</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>08  19  24  26  32  43</t>
+          <t>11  20  23  33  34  44</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000075</v>
+        <v>115000076</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.07.31</t>
+          <t>115.08.04</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>11  20  23  33  34  44</t>
+          <t>04  09  15  30  36  49</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000076</v>
+        <v>115000077</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.08.04</t>
+          <t>115.08.07</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>04  09  15  30  36  49</t>
+          <t>02  12  19  21  25  41</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>31</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000077</v>
+        <v>115000078</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.08.07</t>
+          <t>115.08.11</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>02  12  19  21  25  41</t>
+          <t>08  12  16  24  29  46</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000078</v>
+        <v>115000079</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.08.11</t>
+          <t>115.08.14</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>08  12  16  24  29  46</t>
+          <t>05  12  25  33  34  35</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000079</v>
+        <v>115000080</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.08.14</t>
+          <t>115.08.18</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>05  12  25  33  34  35</t>
+          <t>01  14  25  27  29  43</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>02</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>08/06(四)</t>
+          <t>08/07(五)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>1  0  7</t>
+          <t>9  6  9</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>08/07(五)</t>
+          <t>08/08(六)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>9  6  9</t>
+          <t>2  1  9</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>08/08(六)</t>
+          <t>08/10(一)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2  1  9</t>
+          <t>1  2  4</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>08/10(一)</t>
+          <t>08/11(二)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>1  2  4</t>
+          <t>6  2  3</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>08/11(二)</t>
+          <t>08/12(三)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>6  2  3</t>
+          <t>9  1  0</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>08/12(三)</t>
+          <t>08/13(四)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>9  1  0</t>
+          <t>2  5  7</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>08/13(四)</t>
+          <t>08/14(五)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>2  5  7</t>
+          <t>1  7  7</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>08/14(五)</t>
+          <t>08/15(六)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>1  7  7</t>
+          <t>1  9  5</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>08/15(六)</t>
+          <t>08/17(一)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>1  9  5</t>
+          <t>3  5  4</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>08/17(一)</t>
+          <t>08/18(二)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>3  5  4</t>
+          <t>8  6  8</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>08/06(四)</t>
+          <t>08/07(五)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>6  3  4  5</t>
+          <t>1  1  9  3</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>08/07(五)</t>
+          <t>08/08(六)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>1  1  9  3</t>
+          <t>9  6  2  4</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>08/08(六)</t>
+          <t>08/10(一)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>9  6  2  4</t>
+          <t>3  3  7  5</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>08/10(一)</t>
+          <t>08/11(二)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>3  3  7  5</t>
+          <t>0  2  3  4</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>08/11(二)</t>
+          <t>08/12(三)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>0  2  3  4</t>
+          <t>9  1  3  1</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>08/12(三)</t>
+          <t>08/13(四)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>9  1  3  1</t>
+          <t>5  7  7  0</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>08/13(四)</t>
+          <t>08/14(五)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>5  7  7  0</t>
+          <t>5  4  1  5</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>08/14(五)</t>
+          <t>08/15(六)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>5  4  1  5</t>
+          <t>2  3  9  5</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/15(六)</t>
+          <t>08/17(一)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2  3  9  5</t>
+          <t>6  7  5  3</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/17(一)</t>
+          <t>08/18(二)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>6  7  5  3</t>
+          <t>9  7  8  6</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000191</v>
+        <v>115000192</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.08.07</t>
+          <t>115.08.08</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>06  11  12  13  19</t>
+          <t>05  11  24  31  32</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000192</v>
+        <v>115000193</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.08.08</t>
+          <t>115.08.10</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>05  11  24  31  32</t>
+          <t>01  07  16  23  35</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000193</v>
+        <v>115000194</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.08.10</t>
+          <t>115.08.11</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>01  07  16  23  35</t>
+          <t>07  17  19  23  30</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000194</v>
+        <v>115000195</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.08.11</t>
+          <t>115.08.12</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>07  17  19  23  30</t>
+          <t>07  12  17  20  32</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000195</v>
+        <v>115000196</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.08.12</t>
+          <t>115.08.13</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>07  12  17  20  32</t>
+          <t>05  11  12  17  18</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000196</v>
+        <v>115000197</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.08.13</t>
+          <t>115.08.14</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>05  11  12  17  18</t>
+          <t>07  19  21  25  34</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000197</v>
+        <v>115000198</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.08.14</t>
+          <t>115.08.15</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>07  19  21  25  34</t>
+          <t>12  14  21  35  37</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000198</v>
+        <v>115000199</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.08.15</t>
+          <t>115.08.17</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>12  14  21  35  37</t>
+          <t>19  22  27  28  38</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000199</v>
+        <v>115000200</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.08.17</t>
+          <t>115.08.18</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>19  22  27  28  38</t>
+          <t>05  06  10  28  39</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000200</v>
+        <v>115000201</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.08.18</t>
+          <t>115.08.19</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>05  06  10  28  39</t>
+          <t>02  06  07  32  38</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>08/07(五)</t>
+          <t>08/08(六)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>9  6  9</t>
+          <t>2  1  9</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>08/08(六)</t>
+          <t>08/10(一)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2  1  9</t>
+          <t>1  2  4</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>08/10(一)</t>
+          <t>08/11(二)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>1  2  4</t>
+          <t>6  2  3</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>08/11(二)</t>
+          <t>08/12(三)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>6  2  3</t>
+          <t>9  1  0</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>08/12(三)</t>
+          <t>08/13(四)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>9  1  0</t>
+          <t>2  5  7</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>08/13(四)</t>
+          <t>08/14(五)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2  5  7</t>
+          <t>1  7  7</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>08/14(五)</t>
+          <t>08/15(六)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>1  7  7</t>
+          <t>1  9  5</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>08/15(六)</t>
+          <t>08/17(一)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>1  9  5</t>
+          <t>3  5  4</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>08/17(一)</t>
+          <t>08/18(二)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>3  5  4</t>
+          <t>8  6  8</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>08/18(二)</t>
+          <t>08/19(三)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>8  6  8</t>
+          <t>8  7  4</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>08/07(五)</t>
+          <t>08/08(六)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>1  1  9  3</t>
+          <t>9  6  2  4</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>08/08(六)</t>
+          <t>08/10(一)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>9  6  2  4</t>
+          <t>3  3  7  5</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>08/10(一)</t>
+          <t>08/11(二)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>3  3  7  5</t>
+          <t>0  2  3  4</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>08/11(二)</t>
+          <t>08/12(三)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>0  2  3  4</t>
+          <t>9  1  3  1</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>08/12(三)</t>
+          <t>08/13(四)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>9  1  3  1</t>
+          <t>5  7  7  0</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>08/13(四)</t>
+          <t>08/14(五)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>5  7  7  0</t>
+          <t>5  4  1  5</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>08/14(五)</t>
+          <t>08/15(六)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>5  4  1  5</t>
+          <t>2  3  9  5</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>08/15(六)</t>
+          <t>08/17(一)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2  3  9  5</t>
+          <t>6  7  5  3</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/17(一)</t>
+          <t>08/18(二)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>6  7  5  3</t>
+          <t>9  7  8  6</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/18(二)</t>
+          <t>08/19(三)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>9  7  8  6</t>
+          <t>5  5  5  6</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000192</v>
+        <v>115000193</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.08.08</t>
+          <t>115.08.10</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>05  11  24  31  32</t>
+          <t>01  07  16  23  35</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000193</v>
+        <v>115000194</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.08.10</t>
+          <t>115.08.11</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>01  07  16  23  35</t>
+          <t>07  17  19  23  30</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000194</v>
+        <v>115000195</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.08.11</t>
+          <t>115.08.12</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>07  17  19  23  30</t>
+          <t>07  12  17  20  32</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000195</v>
+        <v>115000196</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.08.12</t>
+          <t>115.08.13</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>07  12  17  20  32</t>
+          <t>05  11  12  17  18</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000196</v>
+        <v>115000197</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.08.13</t>
+          <t>115.08.14</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>05  11  12  17  18</t>
+          <t>07  19  21  25  34</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000197</v>
+        <v>115000198</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.08.14</t>
+          <t>115.08.15</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>07  19  21  25  34</t>
+          <t>12  14  21  35  37</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000198</v>
+        <v>115000199</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.08.15</t>
+          <t>115.08.17</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>12  14  21  35  37</t>
+          <t>19  22  27  28  38</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000199</v>
+        <v>115000200</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.08.17</t>
+          <t>115.08.18</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>19  22  27  28  38</t>
+          <t>05  06  10  28  39</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000200</v>
+        <v>115000201</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.08.18</t>
+          <t>115.08.19</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>05  06  10  28  39</t>
+          <t>02  06  07  32  38</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000201</v>
+        <v>115000202</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.08.19</t>
+          <t>115.08.20</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>02  06  07  32  38</t>
+          <t>04  14  27  32  34</t>
         </is>
       </c>
     </row>
@@ -1354,56 +1354,56 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.07.16</t>
+          <t>115.07.20</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>17  23  25  29  34  36</t>
+          <t>06  12  13  23  29  31</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.07.20</t>
+          <t>115.07.23</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>06  12  13  23  29  31</t>
+          <t>08  10  13  21  29  31</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.07.23</t>
+          <t>115.07.27</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>08  10  13  21  29  31</t>
+          <t>19  22  28  31  33  35</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -1414,16 +1414,16 @@
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.07.27</t>
+          <t>115.07.30</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>19  22  28  31  33  35</t>
+          <t>08  14  17  19  21  23</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -1434,16 +1434,16 @@
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.07.30</t>
+          <t>115.08.03</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>08  14  17  19  21  23</t>
+          <t>04  15  22  26  34  36</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -1454,101 +1454,101 @@
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.08.03</t>
+          <t>115.08.06</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>04  15  22  26  34  36</t>
+          <t>02  07  08  20  26  33</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>04</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.08.06</t>
+          <t>115.08.10</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>02  07  08  20  26  33</t>
+          <t>11  25  28  30  31  36</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.08.10</t>
+          <t>115.08.13</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>11  25  28  30  31  36</t>
+          <t>01  03  04  07  10  19</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.08.13</t>
+          <t>115.08.17</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>01  03  04  07  10  19</t>
+          <t>05  11  18  19  35  38</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>08</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000066</v>
+        <v>115000067</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.08.17</t>
+          <t>115.08.20</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>05  11  18  19  35  38</t>
+          <t>01  02  09  11  29  35</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>02</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>08/08(六)</t>
+          <t>08/10(一)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>2  1  9</t>
+          <t>1  2  4</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>08/10(一)</t>
+          <t>08/11(二)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>1  2  4</t>
+          <t>6  2  3</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>08/11(二)</t>
+          <t>08/12(三)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>6  2  3</t>
+          <t>9  1  0</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>08/12(三)</t>
+          <t>08/13(四)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>9  1  0</t>
+          <t>2  5  7</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>08/13(四)</t>
+          <t>08/14(五)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2  5  7</t>
+          <t>1  7  7</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>08/14(五)</t>
+          <t>08/15(六)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>1  7  7</t>
+          <t>1  9  5</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>08/15(六)</t>
+          <t>08/17(一)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>1  9  5</t>
+          <t>3  5  4</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>08/17(一)</t>
+          <t>08/18(二)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>3  5  4</t>
+          <t>8  6  8</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>08/18(二)</t>
+          <t>08/19(三)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>8  6  8</t>
+          <t>8  7  4</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>08/19(三)</t>
+          <t>08/20(四)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>8  7  4</t>
+          <t>3  4  4</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>08/08(六)</t>
+          <t>08/10(一)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>9  6  2  4</t>
+          <t>3  3  7  5</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>08/10(一)</t>
+          <t>08/11(二)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>3  3  7  5</t>
+          <t>0  2  3  4</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>08/11(二)</t>
+          <t>08/12(三)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>0  2  3  4</t>
+          <t>9  1  3  1</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>08/12(三)</t>
+          <t>08/13(四)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>9  1  3  1</t>
+          <t>5  7  7  0</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>08/13(四)</t>
+          <t>08/14(五)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>5  7  7  0</t>
+          <t>5  4  1  5</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>08/14(五)</t>
+          <t>08/15(六)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>5  4  1  5</t>
+          <t>2  3  9  5</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>08/15(六)</t>
+          <t>08/17(一)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2  3  9  5</t>
+          <t>6  7  5  3</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>08/17(一)</t>
+          <t>08/18(二)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>6  7  5  3</t>
+          <t>9  7  8  6</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/18(二)</t>
+          <t>08/19(三)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>9  7  8  6</t>
+          <t>5  5  5  6</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/19(三)</t>
+          <t>08/20(四)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>5  5  5  6</t>
+          <t>6  8  3  5</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000193</v>
+        <v>115000194</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.08.10</t>
+          <t>115.08.11</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>01  07  16  23  35</t>
+          <t>07  17  19  23  30</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000194</v>
+        <v>115000195</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.08.11</t>
+          <t>115.08.12</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>07  17  19  23  30</t>
+          <t>07  12  17  20  32</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000195</v>
+        <v>115000196</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.08.12</t>
+          <t>115.08.13</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>07  12  17  20  32</t>
+          <t>05  11  12  17  18</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000196</v>
+        <v>115000197</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.08.13</t>
+          <t>115.08.14</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>05  11  12  17  18</t>
+          <t>07  19  21  25  34</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000197</v>
+        <v>115000198</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.08.14</t>
+          <t>115.08.15</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>07  19  21  25  34</t>
+          <t>12  14  21  35  37</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000198</v>
+        <v>115000199</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.08.15</t>
+          <t>115.08.17</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>12  14  21  35  37</t>
+          <t>19  22  27  28  38</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000199</v>
+        <v>115000200</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.08.17</t>
+          <t>115.08.18</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>19  22  27  28  38</t>
+          <t>05  06  10  28  39</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000200</v>
+        <v>115000201</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.08.18</t>
+          <t>115.08.19</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>05  06  10  28  39</t>
+          <t>02  06  07  32  38</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000201</v>
+        <v>115000202</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.08.19</t>
+          <t>115.08.20</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>02  06  07  32  38</t>
+          <t>04  14  27  32  34</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000202</v>
+        <v>115000203</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.08.20</t>
+          <t>115.08.21</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>04  14  27  32  34</t>
+          <t>11  12  18  20  29</t>
         </is>
       </c>
     </row>
@@ -1789,201 +1789,201 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000071</v>
+        <v>115000072</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.07.17</t>
+          <t>115.07.21</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>01  06  12  14  17  26</t>
+          <t>02  08  15  26  35  46</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000072</v>
+        <v>115000073</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.07.21</t>
+          <t>115.07.24</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>02  08  15  26  35  46</t>
+          <t>03  15  27  34  35  44</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000073</v>
+        <v>115000074</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.07.24</t>
+          <t>115.07.28</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>03  15  27  34  35  44</t>
+          <t>08  19  24  26  32  43</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>47</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000074</v>
+        <v>115000075</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.07.28</t>
+          <t>115.07.31</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>08  19  24  26  32  43</t>
+          <t>11  20  23  33  34  44</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000075</v>
+        <v>115000076</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.07.31</t>
+          <t>115.08.04</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>11  20  23  33  34  44</t>
+          <t>04  09  15  30  36  49</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000076</v>
+        <v>115000077</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.08.04</t>
+          <t>115.08.07</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>04  09  15  30  36  49</t>
+          <t>02  12  19  21  25  41</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>31</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000077</v>
+        <v>115000078</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.08.07</t>
+          <t>115.08.11</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>02  12  19  21  25  41</t>
+          <t>08  12  16  24  29  46</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000078</v>
+        <v>115000079</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.08.11</t>
+          <t>115.08.14</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>08  12  16  24  29  46</t>
+          <t>05  12  25  33  34  35</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000079</v>
+        <v>115000080</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.08.14</t>
+          <t>115.08.18</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>05  12  25  33  34  35</t>
+          <t>01  14  25  27  29  43</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000080</v>
+        <v>115000081</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.08.18</t>
+          <t>115.08.21</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>01  14  25  27  29  43</t>
+          <t>08  14  23  24  26  47</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>08/10(一)</t>
+          <t>08/11(二)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>1  2  4</t>
+          <t>6  2  3</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>08/11(二)</t>
+          <t>08/12(三)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>6  2  3</t>
+          <t>9  1  0</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>08/12(三)</t>
+          <t>08/13(四)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>9  1  0</t>
+          <t>2  5  7</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>08/13(四)</t>
+          <t>08/14(五)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2  5  7</t>
+          <t>1  7  7</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>08/14(五)</t>
+          <t>08/15(六)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>1  7  7</t>
+          <t>1  9  5</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>08/15(六)</t>
+          <t>08/17(一)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>1  9  5</t>
+          <t>3  5  4</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>08/17(一)</t>
+          <t>08/18(二)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>3  5  4</t>
+          <t>8  6  8</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>08/18(二)</t>
+          <t>08/19(三)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>8  6  8</t>
+          <t>8  7  4</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>08/19(三)</t>
+          <t>08/20(四)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>8  7  4</t>
+          <t>3  4  4</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>08/20(四)</t>
+          <t>08/21(五)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>3  4  4</t>
+          <t>5  0  2</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>08/10(一)</t>
+          <t>08/11(二)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>3  3  7  5</t>
+          <t>0  2  3  4</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>08/11(二)</t>
+          <t>08/12(三)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>0  2  3  4</t>
+          <t>9  1  3  1</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>08/12(三)</t>
+          <t>08/13(四)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>9  1  3  1</t>
+          <t>5  7  7  0</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>08/13(四)</t>
+          <t>08/14(五)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>5  7  7  0</t>
+          <t>5  4  1  5</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>08/14(五)</t>
+          <t>08/15(六)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>5  4  1  5</t>
+          <t>2  3  9  5</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>08/15(六)</t>
+          <t>08/17(一)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2  3  9  5</t>
+          <t>6  7  5  3</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>08/17(一)</t>
+          <t>08/18(二)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>6  7  5  3</t>
+          <t>9  7  8  6</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>08/18(二)</t>
+          <t>08/19(三)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>9  7  8  6</t>
+          <t>5  5  5  6</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/19(三)</t>
+          <t>08/20(四)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>5  5  5  6</t>
+          <t>6  8  3  5</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/20(四)</t>
+          <t>08/21(五)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>6  8  3  5</t>
+          <t>6  9  1  1</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000194</v>
+        <v>115000195</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.08.11</t>
+          <t>115.08.12</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>07  17  19  23  30</t>
+          <t>07  12  17  20  32</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000195</v>
+        <v>115000196</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.08.12</t>
+          <t>115.08.13</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>07  12  17  20  32</t>
+          <t>05  11  12  17  18</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000196</v>
+        <v>115000197</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.08.13</t>
+          <t>115.08.14</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>05  11  12  17  18</t>
+          <t>07  19  21  25  34</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000197</v>
+        <v>115000198</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.08.14</t>
+          <t>115.08.15</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>07  19  21  25  34</t>
+          <t>12  14  21  35  37</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000198</v>
+        <v>115000199</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.08.15</t>
+          <t>115.08.17</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>12  14  21  35  37</t>
+          <t>19  22  27  28  38</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000199</v>
+        <v>115000200</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.08.17</t>
+          <t>115.08.18</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>19  22  27  28  38</t>
+          <t>05  06  10  28  39</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000200</v>
+        <v>115000201</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.08.18</t>
+          <t>115.08.19</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>05  06  10  28  39</t>
+          <t>02  06  07  32  38</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000201</v>
+        <v>115000202</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.08.19</t>
+          <t>115.08.20</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>02  06  07  32  38</t>
+          <t>04  14  27  32  34</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000202</v>
+        <v>115000203</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.08.20</t>
+          <t>115.08.21</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>04  14  27  32  34</t>
+          <t>11  12  18  20  29</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000203</v>
+        <v>115000204</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.08.21</t>
+          <t>115.08.22</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>11  12  18  20  29</t>
+          <t>09  10  29  30  34</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>08/11(二)</t>
+          <t>08/12(三)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>6  2  3</t>
+          <t>9  1  0</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>08/12(三)</t>
+          <t>08/13(四)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>9  1  0</t>
+          <t>2  5  7</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>08/13(四)</t>
+          <t>08/14(五)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2  5  7</t>
+          <t>1  7  7</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>08/14(五)</t>
+          <t>08/15(六)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>1  7  7</t>
+          <t>1  9  5</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>08/15(六)</t>
+          <t>08/17(一)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>1  9  5</t>
+          <t>3  5  4</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>08/17(一)</t>
+          <t>08/18(二)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>3  5  4</t>
+          <t>8  6  8</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>08/18(二)</t>
+          <t>08/19(三)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>8  6  8</t>
+          <t>8  7  4</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>08/19(三)</t>
+          <t>08/20(四)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>8  7  4</t>
+          <t>3  4  4</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>08/20(四)</t>
+          <t>08/21(五)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>3  4  4</t>
+          <t>5  0  2</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>08/21(五)</t>
+          <t>08/22(六)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>5  0  2</t>
+          <t>3  3  1</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>08/11(二)</t>
+          <t>08/12(三)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>0  2  3  4</t>
+          <t>9  1  3  1</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>08/12(三)</t>
+          <t>08/13(四)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>9  1  3  1</t>
+          <t>5  7  7  0</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>08/13(四)</t>
+          <t>08/14(五)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>5  7  7  0</t>
+          <t>5  4  1  5</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>08/14(五)</t>
+          <t>08/15(六)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>5  4  1  5</t>
+          <t>2  3  9  5</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>08/15(六)</t>
+          <t>08/17(一)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2  3  9  5</t>
+          <t>6  7  5  3</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>08/17(一)</t>
+          <t>08/18(二)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>6  7  5  3</t>
+          <t>9  7  8  6</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>08/18(二)</t>
+          <t>08/19(三)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>9  7  8  6</t>
+          <t>5  5  5  6</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>08/19(三)</t>
+          <t>08/20(四)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>5  5  5  6</t>
+          <t>6  8  3  5</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/20(四)</t>
+          <t>08/21(五)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>6  8  3  5</t>
+          <t>6  9  1  1</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/21(五)</t>
+          <t>08/22(六)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>6  9  1  1</t>
+          <t>5  9  6  2</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000195</v>
+        <v>115000196</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.08.12</t>
+          <t>115.08.13</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>07  12  17  20  32</t>
+          <t>05  11  12  17  18</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000196</v>
+        <v>115000197</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.08.13</t>
+          <t>115.08.14</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>05  11  12  17  18</t>
+          <t>07  19  21  25  34</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000197</v>
+        <v>115000198</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.08.14</t>
+          <t>115.08.15</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>07  19  21  25  34</t>
+          <t>12  14  21  35  37</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000198</v>
+        <v>115000199</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.08.15</t>
+          <t>115.08.17</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>12  14  21  35  37</t>
+          <t>19  22  27  28  38</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000199</v>
+        <v>115000200</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.08.17</t>
+          <t>115.08.18</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>19  22  27  28  38</t>
+          <t>05  06  10  28  39</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000200</v>
+        <v>115000201</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.08.18</t>
+          <t>115.08.19</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>05  06  10  28  39</t>
+          <t>02  06  07  32  38</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000201</v>
+        <v>115000202</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.08.19</t>
+          <t>115.08.20</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>02  06  07  32  38</t>
+          <t>04  14  27  32  34</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000202</v>
+        <v>115000203</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.08.20</t>
+          <t>115.08.21</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>04  14  27  32  34</t>
+          <t>11  12  18  20  29</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000203</v>
+        <v>115000204</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.08.21</t>
+          <t>115.08.22</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>11  12  18  20  29</t>
+          <t>09  10  29  30  34</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000204</v>
+        <v>115000205</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.08.22</t>
+          <t>115.08.24</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>09  10  29  30  34</t>
+          <t>09  10  19  23  26</t>
         </is>
       </c>
     </row>
@@ -1354,36 +1354,36 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.07.20</t>
+          <t>115.07.23</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>06  12  13  23  29  31</t>
+          <t>08  10  13  21  29  31</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.07.23</t>
+          <t>115.07.27</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>08  10  13  21  29  31</t>
+          <t>19  22  28  31  33  35</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -1394,16 +1394,16 @@
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.07.27</t>
+          <t>115.07.30</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>19  22  28  31  33  35</t>
+          <t>08  14  17  19  21  23</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -1414,16 +1414,16 @@
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.07.30</t>
+          <t>115.08.03</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>08  14  17  19  21  23</t>
+          <t>04  15  22  26  34  36</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -1434,121 +1434,121 @@
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.08.03</t>
+          <t>115.08.06</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>04  15  22  26  34  36</t>
+          <t>02  07  08  20  26  33</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>04</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.08.06</t>
+          <t>115.08.10</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>02  07  08  20  26  33</t>
+          <t>11  25  28  30  31  36</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.08.10</t>
+          <t>115.08.13</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>11  25  28  30  31  36</t>
+          <t>01  03  04  07  10  19</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.08.13</t>
+          <t>115.08.17</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>01  03  04  07  10  19</t>
+          <t>05  11  18  19  35  38</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>08</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000066</v>
+        <v>115000067</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.08.17</t>
+          <t>115.08.20</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>05  11  18  19  35  38</t>
+          <t>01  02  09  11  29  35</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000067</v>
+        <v>115000068</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.08.20</t>
+          <t>115.08.24</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>01  02  09  11  29  35</t>
+          <t>06  07  09  23  26  36</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>07</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>08/12(三)</t>
+          <t>08/13(四)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>9  1  0</t>
+          <t>2  5  7</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>08/13(四)</t>
+          <t>08/14(五)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2  5  7</t>
+          <t>1  7  7</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>08/14(五)</t>
+          <t>08/15(六)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>1  7  7</t>
+          <t>1  9  5</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>08/15(六)</t>
+          <t>08/17(一)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>1  9  5</t>
+          <t>3  5  4</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>08/17(一)</t>
+          <t>08/18(二)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>3  5  4</t>
+          <t>8  6  8</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>08/18(二)</t>
+          <t>08/19(三)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>8  6  8</t>
+          <t>8  7  4</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>08/19(三)</t>
+          <t>08/20(四)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>8  7  4</t>
+          <t>3  4  4</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>08/20(四)</t>
+          <t>08/21(五)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>3  4  4</t>
+          <t>5  0  2</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>08/21(五)</t>
+          <t>08/22(六)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>5  0  2</t>
+          <t>3  3  1</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>08/22(六)</t>
+          <t>08/24(一)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>3  3  1</t>
+          <t>5  7  2</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>08/12(三)</t>
+          <t>08/13(四)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>9  1  3  1</t>
+          <t>5  7  7  0</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>08/13(四)</t>
+          <t>08/14(五)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>5  7  7  0</t>
+          <t>5  4  1  5</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>08/14(五)</t>
+          <t>08/15(六)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>5  4  1  5</t>
+          <t>2  3  9  5</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>08/15(六)</t>
+          <t>08/17(一)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2  3  9  5</t>
+          <t>6  7  5  3</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>08/17(一)</t>
+          <t>08/18(二)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>6  7  5  3</t>
+          <t>9  7  8  6</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>08/18(二)</t>
+          <t>08/19(三)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>9  7  8  6</t>
+          <t>5  5  5  6</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>08/19(三)</t>
+          <t>08/20(四)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>5  5  5  6</t>
+          <t>6  8  3  5</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>08/20(四)</t>
+          <t>08/21(五)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>6  8  3  5</t>
+          <t>6  9  1  1</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/21(五)</t>
+          <t>08/22(六)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>6  9  1  1</t>
+          <t>5  9  6  2</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/22(六)</t>
+          <t>08/24(一)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>5  9  6  2</t>
+          <t>3  0  1  7</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000196</v>
+        <v>115000197</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.08.13</t>
+          <t>115.08.14</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>05  11  12  17  18</t>
+          <t>07  19  21  25  34</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000197</v>
+        <v>115000198</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.08.14</t>
+          <t>115.08.15</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>07  19  21  25  34</t>
+          <t>12  14  21  35  37</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000198</v>
+        <v>115000199</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.08.15</t>
+          <t>115.08.17</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>12  14  21  35  37</t>
+          <t>19  22  27  28  38</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000199</v>
+        <v>115000200</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.08.17</t>
+          <t>115.08.18</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>19  22  27  28  38</t>
+          <t>05  06  10  28  39</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000200</v>
+        <v>115000201</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.08.18</t>
+          <t>115.08.19</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>05  06  10  28  39</t>
+          <t>02  06  07  32  38</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000201</v>
+        <v>115000202</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.08.19</t>
+          <t>115.08.20</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>02  06  07  32  38</t>
+          <t>04  14  27  32  34</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000202</v>
+        <v>115000203</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.08.20</t>
+          <t>115.08.21</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>04  14  27  32  34</t>
+          <t>11  12  18  20  29</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000203</v>
+        <v>115000204</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.08.21</t>
+          <t>115.08.22</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>11  12  18  20  29</t>
+          <t>09  10  29  30  34</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000204</v>
+        <v>115000205</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.08.22</t>
+          <t>115.08.24</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>09  10  29  30  34</t>
+          <t>09  10  19  23  26</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000205</v>
+        <v>115000206</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.08.24</t>
+          <t>115.08.25</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>09  10  19  23  26</t>
+          <t>08  21  23  30  35</t>
         </is>
       </c>
     </row>
@@ -1789,201 +1789,201 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000072</v>
+        <v>115000073</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.07.21</t>
+          <t>115.07.24</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>02  08  15  26  35  46</t>
+          <t>03  15  27  34  35  44</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000073</v>
+        <v>115000074</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.07.24</t>
+          <t>115.07.28</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>03  15  27  34  35  44</t>
+          <t>08  19  24  26  32  43</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>47</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000074</v>
+        <v>115000075</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.07.28</t>
+          <t>115.07.31</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>08  19  24  26  32  43</t>
+          <t>11  20  23  33  34  44</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000075</v>
+        <v>115000076</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.07.31</t>
+          <t>115.08.04</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>11  20  23  33  34  44</t>
+          <t>04  09  15  30  36  49</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000076</v>
+        <v>115000077</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.08.04</t>
+          <t>115.08.07</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>04  09  15  30  36  49</t>
+          <t>02  12  19  21  25  41</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>31</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000077</v>
+        <v>115000078</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.08.07</t>
+          <t>115.08.11</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>02  12  19  21  25  41</t>
+          <t>08  12  16  24  29  46</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000078</v>
+        <v>115000079</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.08.11</t>
+          <t>115.08.14</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>08  12  16  24  29  46</t>
+          <t>05  12  25  33  34  35</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000079</v>
+        <v>115000080</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.08.14</t>
+          <t>115.08.18</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>05  12  25  33  34  35</t>
+          <t>01  14  25  27  29  43</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000080</v>
+        <v>115000081</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.08.18</t>
+          <t>115.08.21</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>01  14  25  27  29  43</t>
+          <t>08  14  23  24  26  47</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000081</v>
+        <v>115000082</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.08.21</t>
+          <t>115.08.25</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>08  14  23  24  26  47</t>
+          <t>12  24  26  32  35  40</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>06</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>08/13(四)</t>
+          <t>08/14(五)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>2  5  7</t>
+          <t>1  7  7</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>08/14(五)</t>
+          <t>08/15(六)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>1  7  7</t>
+          <t>1  9  5</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>08/15(六)</t>
+          <t>08/17(一)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>1  9  5</t>
+          <t>3  5  4</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>08/17(一)</t>
+          <t>08/18(二)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>3  5  4</t>
+          <t>8  6  8</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>08/18(二)</t>
+          <t>08/19(三)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>8  6  8</t>
+          <t>8  7  4</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>08/19(三)</t>
+          <t>08/20(四)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>8  7  4</t>
+          <t>3  4  4</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>08/20(四)</t>
+          <t>08/21(五)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>3  4  4</t>
+          <t>5  0  2</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>08/21(五)</t>
+          <t>08/22(六)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>5  0  2</t>
+          <t>3  3  1</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>08/22(六)</t>
+          <t>08/24(一)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>3  3  1</t>
+          <t>5  7  2</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>08/24(一)</t>
+          <t>08/25(二)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>5  7  2</t>
+          <t>8  7  2</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>08/13(四)</t>
+          <t>08/14(五)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>5  7  7  0</t>
+          <t>5  4  1  5</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>08/14(五)</t>
+          <t>08/15(六)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>5  4  1  5</t>
+          <t>2  3  9  5</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>08/15(六)</t>
+          <t>08/17(一)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2  3  9  5</t>
+          <t>6  7  5  3</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>08/17(一)</t>
+          <t>08/18(二)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>6  7  5  3</t>
+          <t>9  7  8  6</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>08/18(二)</t>
+          <t>08/19(三)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>9  7  8  6</t>
+          <t>5  5  5  6</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>08/19(三)</t>
+          <t>08/20(四)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>5  5  5  6</t>
+          <t>6  8  3  5</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>08/20(四)</t>
+          <t>08/21(五)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>6  8  3  5</t>
+          <t>6  9  1  1</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>08/21(五)</t>
+          <t>08/22(六)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>6  9  1  1</t>
+          <t>5  9  6  2</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/22(六)</t>
+          <t>08/24(一)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>5  9  6  2</t>
+          <t>3  0  1  7</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/24(一)</t>
+          <t>08/25(二)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>3  0  1  7</t>
+          <t>7  0  6  7</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000197</v>
+        <v>115000198</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.08.14</t>
+          <t>115.08.15</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>07  19  21  25  34</t>
+          <t>12  14  21  35  37</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000198</v>
+        <v>115000199</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.08.15</t>
+          <t>115.08.17</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>12  14  21  35  37</t>
+          <t>19  22  27  28  38</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000199</v>
+        <v>115000200</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.08.17</t>
+          <t>115.08.18</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>19  22  27  28  38</t>
+          <t>05  06  10  28  39</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000200</v>
+        <v>115000201</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.08.18</t>
+          <t>115.08.19</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>05  06  10  28  39</t>
+          <t>02  06  07  32  38</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000201</v>
+        <v>115000202</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.08.19</t>
+          <t>115.08.20</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>02  06  07  32  38</t>
+          <t>04  14  27  32  34</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000202</v>
+        <v>115000203</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.08.20</t>
+          <t>115.08.21</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>04  14  27  32  34</t>
+          <t>11  12  18  20  29</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000203</v>
+        <v>115000204</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.08.21</t>
+          <t>115.08.22</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>11  12  18  20  29</t>
+          <t>09  10  29  30  34</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000204</v>
+        <v>115000205</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.08.22</t>
+          <t>115.08.24</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>09  10  29  30  34</t>
+          <t>09  10  19  23  26</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000205</v>
+        <v>115000206</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.08.24</t>
+          <t>115.08.25</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>09  10  19  23  26</t>
+          <t>08  21  23  30  35</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000206</v>
+        <v>115000207</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.08.25</t>
+          <t>115.08.26</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>08  21  23  30  35</t>
+          <t>13  19  23  35  38</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>08/14(五)</t>
+          <t>08/15(六)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>1  7  7</t>
+          <t>1  9  5</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>08/15(六)</t>
+          <t>08/17(一)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>1  9  5</t>
+          <t>3  5  4</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>08/17(一)</t>
+          <t>08/18(二)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>3  5  4</t>
+          <t>8  6  8</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>08/18(二)</t>
+          <t>08/19(三)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>8  6  8</t>
+          <t>8  7  4</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>08/19(三)</t>
+          <t>08/20(四)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>8  7  4</t>
+          <t>3  4  4</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>08/20(四)</t>
+          <t>08/21(五)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>3  4  4</t>
+          <t>5  0  2</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>08/21(五)</t>
+          <t>08/22(六)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>5  0  2</t>
+          <t>3  3  1</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>08/22(六)</t>
+          <t>08/24(一)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>3  3  1</t>
+          <t>5  7  2</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>08/24(一)</t>
+          <t>08/25(二)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>5  7  2</t>
+          <t>8  7  2</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>08/25(二)</t>
+          <t>08/26(三)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>8  7  2</t>
+          <t>4  3  2</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>08/14(五)</t>
+          <t>08/15(六)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>5  4  1  5</t>
+          <t>2  3  9  5</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>08/15(六)</t>
+          <t>08/17(一)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2  3  9  5</t>
+          <t>6  7  5  3</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>08/17(一)</t>
+          <t>08/18(二)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>6  7  5  3</t>
+          <t>9  7  8  6</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>08/18(二)</t>
+          <t>08/19(三)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>9  7  8  6</t>
+          <t>5  5  5  6</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>08/19(三)</t>
+          <t>08/20(四)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>5  5  5  6</t>
+          <t>6  8  3  5</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>08/20(四)</t>
+          <t>08/21(五)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>6  8  3  5</t>
+          <t>6  9  1  1</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>08/21(五)</t>
+          <t>08/22(六)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>6  9  1  1</t>
+          <t>5  9  6  2</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>08/22(六)</t>
+          <t>08/24(一)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>5  9  6  2</t>
+          <t>3  0  1  7</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/24(一)</t>
+          <t>08/25(二)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>3  0  1  7</t>
+          <t>7  0  6  7</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/25(二)</t>
+          <t>08/26(三)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>7  0  6  7</t>
+          <t>6  3  3  9</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000198</v>
+        <v>115000199</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.08.15</t>
+          <t>115.08.17</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>12  14  21  35  37</t>
+          <t>19  22  27  28  38</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000199</v>
+        <v>115000200</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.08.17</t>
+          <t>115.08.18</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>19  22  27  28  38</t>
+          <t>05  06  10  28  39</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000200</v>
+        <v>115000201</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.08.18</t>
+          <t>115.08.19</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>05  06  10  28  39</t>
+          <t>02  06  07  32  38</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000201</v>
+        <v>115000202</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.08.19</t>
+          <t>115.08.20</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>02  06  07  32  38</t>
+          <t>04  14  27  32  34</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000202</v>
+        <v>115000203</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.08.20</t>
+          <t>115.08.21</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>04  14  27  32  34</t>
+          <t>11  12  18  20  29</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000203</v>
+        <v>115000204</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.08.21</t>
+          <t>115.08.22</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>11  12  18  20  29</t>
+          <t>09  10  29  30  34</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000204</v>
+        <v>115000205</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.08.22</t>
+          <t>115.08.24</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>09  10  29  30  34</t>
+          <t>09  10  19  23  26</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000205</v>
+        <v>115000206</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.08.24</t>
+          <t>115.08.25</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>09  10  19  23  26</t>
+          <t>08  21  23  30  35</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000206</v>
+        <v>115000207</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.08.25</t>
+          <t>115.08.26</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>08  21  23  30  35</t>
+          <t>13  19  23  35  38</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000207</v>
+        <v>115000208</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.08.26</t>
+          <t>115.08.27</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>13  19  23  35  38</t>
+          <t>02  03  07  25  33</t>
         </is>
       </c>
     </row>
@@ -1354,16 +1354,16 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.07.23</t>
+          <t>115.07.27</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>08  10  13  21  29  31</t>
+          <t>19  22  28  31  33  35</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
@@ -1374,16 +1374,16 @@
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.07.27</t>
+          <t>115.07.30</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>19  22  28  31  33  35</t>
+          <t>08  14  17  19  21  23</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -1394,16 +1394,16 @@
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.07.30</t>
+          <t>115.08.03</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>08  14  17  19  21  23</t>
+          <t>04  15  22  26  34  36</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -1414,141 +1414,141 @@
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.08.03</t>
+          <t>115.08.06</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>04  15  22  26  34  36</t>
+          <t>02  07  08  20  26  33</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>04</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.08.06</t>
+          <t>115.08.10</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>02  07  08  20  26  33</t>
+          <t>11  25  28  30  31  36</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.08.10</t>
+          <t>115.08.13</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>11  25  28  30  31  36</t>
+          <t>01  03  04  07  10  19</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.08.13</t>
+          <t>115.08.17</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>01  03  04  07  10  19</t>
+          <t>05  11  18  19  35  38</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>08</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000066</v>
+        <v>115000067</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.08.17</t>
+          <t>115.08.20</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>05  11  18  19  35  38</t>
+          <t>01  02  09  11  29  35</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000067</v>
+        <v>115000068</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.08.20</t>
+          <t>115.08.24</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>01  02  09  11  29  35</t>
+          <t>06  07  09  23  26  36</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000068</v>
+        <v>115000069</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.08.24</t>
+          <t>115.08.27</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>06  07  09  23  26  36</t>
+          <t>02  07  09  11  24  36</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>01</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>08/15(六)</t>
+          <t>08/17(一)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>1  9  5</t>
+          <t>3  5  4</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>08/17(一)</t>
+          <t>08/18(二)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>3  5  4</t>
+          <t>8  6  8</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>08/18(二)</t>
+          <t>08/19(三)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>8  6  8</t>
+          <t>8  7  4</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>08/19(三)</t>
+          <t>08/20(四)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>8  7  4</t>
+          <t>3  4  4</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>08/20(四)</t>
+          <t>08/21(五)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>3  4  4</t>
+          <t>5  0  2</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>08/21(五)</t>
+          <t>08/22(六)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>5  0  2</t>
+          <t>3  3  1</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>08/22(六)</t>
+          <t>08/24(一)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>3  3  1</t>
+          <t>5  7  2</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>08/24(一)</t>
+          <t>08/25(二)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>5  7  2</t>
+          <t>8  7  2</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>08/25(二)</t>
+          <t>08/26(三)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>8  7  2</t>
+          <t>4  3  2</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>08/26(三)</t>
+          <t>08/27(四)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>4  3  2</t>
+          <t>8  9  1</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>08/15(六)</t>
+          <t>08/17(一)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2  3  9  5</t>
+          <t>6  7  5  3</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>08/17(一)</t>
+          <t>08/18(二)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>6  7  5  3</t>
+          <t>9  7  8  6</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>08/18(二)</t>
+          <t>08/19(三)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>9  7  8  6</t>
+          <t>5  5  5  6</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>08/19(三)</t>
+          <t>08/20(四)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>5  5  5  6</t>
+          <t>6  8  3  5</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>08/20(四)</t>
+          <t>08/21(五)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>6  8  3  5</t>
+          <t>6  9  1  1</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>08/21(五)</t>
+          <t>08/22(六)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>6  9  1  1</t>
+          <t>5  9  6  2</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>08/22(六)</t>
+          <t>08/24(一)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>5  9  6  2</t>
+          <t>3  0  1  7</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>08/24(一)</t>
+          <t>08/25(二)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>3  0  1  7</t>
+          <t>7  0  6  7</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/25(二)</t>
+          <t>08/26(三)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>7  0  6  7</t>
+          <t>6  3  3  9</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/26(三)</t>
+          <t>08/27(四)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>6  3  3  9</t>
+          <t>6  2  1  7</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000199</v>
+        <v>115000200</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.08.17</t>
+          <t>115.08.18</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>19  22  27  28  38</t>
+          <t>05  06  10  28  39</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000200</v>
+        <v>115000201</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.08.18</t>
+          <t>115.08.19</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>05  06  10  28  39</t>
+          <t>02  06  07  32  38</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000201</v>
+        <v>115000202</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.08.19</t>
+          <t>115.08.20</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>02  06  07  32  38</t>
+          <t>04  14  27  32  34</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000202</v>
+        <v>115000203</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.08.20</t>
+          <t>115.08.21</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>04  14  27  32  34</t>
+          <t>11  12  18  20  29</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000203</v>
+        <v>115000204</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.08.21</t>
+          <t>115.08.22</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>11  12  18  20  29</t>
+          <t>09  10  29  30  34</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000204</v>
+        <v>115000205</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.08.22</t>
+          <t>115.08.24</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>09  10  29  30  34</t>
+          <t>09  10  19  23  26</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000205</v>
+        <v>115000206</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.08.24</t>
+          <t>115.08.25</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>09  10  19  23  26</t>
+          <t>08  21  23  30  35</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000206</v>
+        <v>115000207</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.08.25</t>
+          <t>115.08.26</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>08  21  23  30  35</t>
+          <t>13  19  23  35  38</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000207</v>
+        <v>115000208</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.08.26</t>
+          <t>115.08.27</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>13  19  23  35  38</t>
+          <t>02  03  07  25  33</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000208</v>
+        <v>115000209</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.08.27</t>
+          <t>115.08.28</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>02  03  07  25  33</t>
+          <t>02  04  09  12  36</t>
         </is>
       </c>
     </row>
@@ -1789,201 +1789,201 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000073</v>
+        <v>115000074</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.07.24</t>
+          <t>115.07.28</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>03  15  27  34  35  44</t>
+          <t>08  19  24  26  32  43</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>47</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000074</v>
+        <v>115000075</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.07.28</t>
+          <t>115.07.31</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>08  19  24  26  32  43</t>
+          <t>11  20  23  33  34  44</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000075</v>
+        <v>115000076</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.07.31</t>
+          <t>115.08.04</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>11  20  23  33  34  44</t>
+          <t>04  09  15  30  36  49</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000076</v>
+        <v>115000077</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.08.04</t>
+          <t>115.08.07</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>04  09  15  30  36  49</t>
+          <t>02  12  19  21  25  41</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>31</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000077</v>
+        <v>115000078</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.08.07</t>
+          <t>115.08.11</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>02  12  19  21  25  41</t>
+          <t>08  12  16  24  29  46</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000078</v>
+        <v>115000079</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.08.11</t>
+          <t>115.08.14</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>08  12  16  24  29  46</t>
+          <t>05  12  25  33  34  35</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000079</v>
+        <v>115000080</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.08.14</t>
+          <t>115.08.18</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>05  12  25  33  34  35</t>
+          <t>01  14  25  27  29  43</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000080</v>
+        <v>115000081</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.08.18</t>
+          <t>115.08.21</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>01  14  25  27  29  43</t>
+          <t>08  14  23  24  26  47</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000081</v>
+        <v>115000082</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.08.21</t>
+          <t>115.08.25</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>08  14  23  24  26  47</t>
+          <t>12  24  26  32  35  40</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000082</v>
+        <v>115000083</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.08.25</t>
+          <t>115.08.28</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>12  24  26  32  35  40</t>
+          <t>09  20  23  26  36  44</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>04</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>08/17(一)</t>
+          <t>08/18(二)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>3  5  4</t>
+          <t>8  6  8</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>08/18(二)</t>
+          <t>08/19(三)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>8  6  8</t>
+          <t>8  7  4</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>08/19(三)</t>
+          <t>08/20(四)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>8  7  4</t>
+          <t>3  4  4</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>08/20(四)</t>
+          <t>08/21(五)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>3  4  4</t>
+          <t>5  0  2</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>08/21(五)</t>
+          <t>08/22(六)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>5  0  2</t>
+          <t>3  3  1</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>08/22(六)</t>
+          <t>08/24(一)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>3  3  1</t>
+          <t>5  7  2</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>08/24(一)</t>
+          <t>08/25(二)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>5  7  2</t>
+          <t>8  7  2</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>08/25(二)</t>
+          <t>08/26(三)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>8  7  2</t>
+          <t>4  3  2</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>08/26(三)</t>
+          <t>08/27(四)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>4  3  2</t>
+          <t>8  9  1</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>08/27(四)</t>
+          <t>08/28(五)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>8  9  1</t>
+          <t>8  2  9</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>08/17(一)</t>
+          <t>08/18(二)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>6  7  5  3</t>
+          <t>9  7  8  6</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>08/18(二)</t>
+          <t>08/19(三)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>9  7  8  6</t>
+          <t>5  5  5  6</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>08/19(三)</t>
+          <t>08/20(四)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>5  5  5  6</t>
+          <t>6  8  3  5</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>08/20(四)</t>
+          <t>08/21(五)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>6  8  3  5</t>
+          <t>6  9  1  1</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>08/21(五)</t>
+          <t>08/22(六)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>6  9  1  1</t>
+          <t>5  9  6  2</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>08/22(六)</t>
+          <t>08/24(一)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>5  9  6  2</t>
+          <t>3  0  1  7</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>08/24(一)</t>
+          <t>08/25(二)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>3  0  1  7</t>
+          <t>7  0  6  7</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>08/25(二)</t>
+          <t>08/26(三)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>7  0  6  7</t>
+          <t>6  3  3  9</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/26(三)</t>
+          <t>08/27(四)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>6  3  3  9</t>
+          <t>6  2  1  7</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/27(四)</t>
+          <t>08/28(五)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>6  2  1  7</t>
+          <t>1  1  1  9</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000200</v>
+        <v>115000201</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.08.18</t>
+          <t>115.08.19</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>05  06  10  28  39</t>
+          <t>02  06  07  32  38</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000201</v>
+        <v>115000202</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.08.19</t>
+          <t>115.08.20</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>02  06  07  32  38</t>
+          <t>04  14  27  32  34</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000202</v>
+        <v>115000203</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.08.20</t>
+          <t>115.08.21</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>04  14  27  32  34</t>
+          <t>11  12  18  20  29</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000203</v>
+        <v>115000204</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.08.21</t>
+          <t>115.08.22</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>11  12  18  20  29</t>
+          <t>09  10  29  30  34</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000204</v>
+        <v>115000205</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.08.22</t>
+          <t>115.08.24</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>09  10  29  30  34</t>
+          <t>09  10  19  23  26</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000205</v>
+        <v>115000206</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.08.24</t>
+          <t>115.08.25</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>09  10  19  23  26</t>
+          <t>08  21  23  30  35</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000206</v>
+        <v>115000207</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.08.25</t>
+          <t>115.08.26</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>08  21  23  30  35</t>
+          <t>13  19  23  35  38</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000207</v>
+        <v>115000208</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.08.26</t>
+          <t>115.08.27</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>13  19  23  35  38</t>
+          <t>02  03  07  25  33</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000208</v>
+        <v>115000209</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.08.27</t>
+          <t>115.08.28</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>02  03  07  25  33</t>
+          <t>02  04  09  12  36</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000209</v>
+        <v>115000210</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.08.28</t>
+          <t>115.08.29</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>02  04  09  12  36</t>
+          <t>03  06  17  23  33</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>08/18(二)</t>
+          <t>08/19(三)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>8  6  8</t>
+          <t>8  7  4</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>08/19(三)</t>
+          <t>08/20(四)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>8  7  4</t>
+          <t>3  4  4</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>08/20(四)</t>
+          <t>08/21(五)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>3  4  4</t>
+          <t>5  0  2</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>08/21(五)</t>
+          <t>08/22(六)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>5  0  2</t>
+          <t>3  3  1</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>08/22(六)</t>
+          <t>08/24(一)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>3  3  1</t>
+          <t>5  7  2</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>08/24(一)</t>
+          <t>08/25(二)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>5  7  2</t>
+          <t>8  7  2</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>08/25(二)</t>
+          <t>08/26(三)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>8  7  2</t>
+          <t>4  3  2</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>08/26(三)</t>
+          <t>08/27(四)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>4  3  2</t>
+          <t>8  9  1</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>08/27(四)</t>
+          <t>08/28(五)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>8  9  1</t>
+          <t>8  2  9</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>08/28(五)</t>
+          <t>08/29(六)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>8  2  9</t>
+          <t>8  7  0</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>08/18(二)</t>
+          <t>08/19(三)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>9  7  8  6</t>
+          <t>5  5  5  6</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>08/19(三)</t>
+          <t>08/20(四)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>5  5  5  6</t>
+          <t>6  8  3  5</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>08/20(四)</t>
+          <t>08/21(五)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>6  8  3  5</t>
+          <t>6  9  1  1</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>08/21(五)</t>
+          <t>08/22(六)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>6  9  1  1</t>
+          <t>5  9  6  2</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>08/22(六)</t>
+          <t>08/24(一)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>5  9  6  2</t>
+          <t>3  0  1  7</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>08/24(一)</t>
+          <t>08/25(二)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>3  0  1  7</t>
+          <t>7  0  6  7</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>08/25(二)</t>
+          <t>08/26(三)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>7  0  6  7</t>
+          <t>6  3  3  9</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>08/26(三)</t>
+          <t>08/27(四)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>6  3  3  9</t>
+          <t>6  2  1  7</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/27(四)</t>
+          <t>08/28(五)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>6  2  1  7</t>
+          <t>1  1  1  9</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/28(五)</t>
+          <t>08/29(六)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>1  1  1  9</t>
+          <t>1  2  8  0</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000201</v>
+        <v>115000202</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.08.19</t>
+          <t>115.08.20</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>02  06  07  32  38</t>
+          <t>04  14  27  32  34</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000202</v>
+        <v>115000203</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.08.20</t>
+          <t>115.08.21</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>04  14  27  32  34</t>
+          <t>11  12  18  20  29</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000203</v>
+        <v>115000204</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.08.21</t>
+          <t>115.08.22</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>11  12  18  20  29</t>
+          <t>09  10  29  30  34</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000204</v>
+        <v>115000205</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.08.22</t>
+          <t>115.08.24</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>09  10  29  30  34</t>
+          <t>09  10  19  23  26</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000205</v>
+        <v>115000206</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.08.24</t>
+          <t>115.08.25</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>09  10  19  23  26</t>
+          <t>08  21  23  30  35</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000206</v>
+        <v>115000207</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.08.25</t>
+          <t>115.08.26</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>08  21  23  30  35</t>
+          <t>13  19  23  35  38</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000207</v>
+        <v>115000208</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.08.26</t>
+          <t>115.08.27</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>13  19  23  35  38</t>
+          <t>02  03  07  25  33</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000208</v>
+        <v>115000209</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.08.27</t>
+          <t>115.08.28</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>02  03  07  25  33</t>
+          <t>02  04  09  12  36</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000209</v>
+        <v>115000210</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.08.28</t>
+          <t>115.08.29</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>02  04  09  12  36</t>
+          <t>03  06  17  23  33</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000210</v>
+        <v>115000211</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.08.29</t>
+          <t>115.08.31</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>03  06  17  23  33</t>
+          <t>05  10  12  33  39</t>
         </is>
       </c>
     </row>
@@ -1354,16 +1354,16 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.07.27</t>
+          <t>115.07.30</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>19  22  28  31  33  35</t>
+          <t>08  14  17  19  21  23</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
@@ -1374,16 +1374,16 @@
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.07.30</t>
+          <t>115.08.03</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>08  14  17  19  21  23</t>
+          <t>04  15  22  26  34  36</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -1394,161 +1394,161 @@
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.08.03</t>
+          <t>115.08.06</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>04  15  22  26  34  36</t>
+          <t>02  07  08  20  26  33</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>04</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.08.06</t>
+          <t>115.08.10</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>02  07  08  20  26  33</t>
+          <t>11  25  28  30  31  36</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.08.10</t>
+          <t>115.08.13</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>11  25  28  30  31  36</t>
+          <t>01  03  04  07  10  19</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.08.13</t>
+          <t>115.08.17</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>01  03  04  07  10  19</t>
+          <t>05  11  18  19  35  38</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>08</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000066</v>
+        <v>115000067</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.08.17</t>
+          <t>115.08.20</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>05  11  18  19  35  38</t>
+          <t>01  02  09  11  29  35</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000067</v>
+        <v>115000068</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.08.20</t>
+          <t>115.08.24</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>01  02  09  11  29  35</t>
+          <t>06  07  09  23  26  36</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000068</v>
+        <v>115000069</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.08.24</t>
+          <t>115.08.27</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>06  07  09  23  26  36</t>
+          <t>02  07  09  11  24  36</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>01</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000069</v>
+        <v>115000070</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.08.27</t>
+          <t>115.08.31</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>02  07  09  11  24  36</t>
+          <t>04  08  12  19  32  37</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>08/19(三)</t>
+          <t>08/20(四)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>8  7  4</t>
+          <t>3  4  4</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>08/20(四)</t>
+          <t>08/21(五)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>3  4  4</t>
+          <t>5  0  2</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>08/21(五)</t>
+          <t>08/22(六)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>5  0  2</t>
+          <t>3  3  1</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>08/22(六)</t>
+          <t>08/24(一)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>3  3  1</t>
+          <t>5  7  2</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>08/24(一)</t>
+          <t>08/25(二)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>5  7  2</t>
+          <t>8  7  2</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>08/25(二)</t>
+          <t>08/26(三)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>8  7  2</t>
+          <t>4  3  2</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>08/26(三)</t>
+          <t>08/27(四)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>4  3  2</t>
+          <t>8  9  1</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>08/27(四)</t>
+          <t>08/28(五)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>8  9  1</t>
+          <t>8  2  9</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>08/28(五)</t>
+          <t>08/29(六)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>8  2  9</t>
+          <t>8  7  0</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>08/29(六)</t>
+          <t>08/31(一)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>8  7  0</t>
+          <t>8  5  7</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>08/19(三)</t>
+          <t>08/20(四)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>5  5  5  6</t>
+          <t>6  8  3  5</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>08/20(四)</t>
+          <t>08/21(五)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>6  8  3  5</t>
+          <t>6  9  1  1</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>08/21(五)</t>
+          <t>08/22(六)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>6  9  1  1</t>
+          <t>5  9  6  2</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>08/22(六)</t>
+          <t>08/24(一)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>5  9  6  2</t>
+          <t>3  0  1  7</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>08/24(一)</t>
+          <t>08/25(二)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>3  0  1  7</t>
+          <t>7  0  6  7</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>08/25(二)</t>
+          <t>08/26(三)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>7  0  6  7</t>
+          <t>6  3  3  9</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>08/26(三)</t>
+          <t>08/27(四)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>6  3  3  9</t>
+          <t>6  2  1  7</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>08/27(四)</t>
+          <t>08/28(五)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>6  2  1  7</t>
+          <t>1  1  1  9</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/28(五)</t>
+          <t>08/29(六)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>1  1  1  9</t>
+          <t>1  2  8  0</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/29(六)</t>
+          <t>08/31(一)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>1  2  8  0</t>
+          <t>0  4  2  7</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000202</v>
+        <v>115000203</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.08.20</t>
+          <t>115.08.21</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>04  14  27  32  34</t>
+          <t>11  12  18  20  29</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000203</v>
+        <v>115000204</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.08.21</t>
+          <t>115.08.22</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>11  12  18  20  29</t>
+          <t>09  10  29  30  34</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000204</v>
+        <v>115000205</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.08.22</t>
+          <t>115.08.24</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>09  10  29  30  34</t>
+          <t>09  10  19  23  26</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000205</v>
+        <v>115000206</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.08.24</t>
+          <t>115.08.25</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>09  10  19  23  26</t>
+          <t>08  21  23  30  35</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000206</v>
+        <v>115000207</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.08.25</t>
+          <t>115.08.26</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>08  21  23  30  35</t>
+          <t>13  19  23  35  38</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000207</v>
+        <v>115000208</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.08.26</t>
+          <t>115.08.27</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>13  19  23  35  38</t>
+          <t>02  03  07  25  33</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000208</v>
+        <v>115000209</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.08.27</t>
+          <t>115.08.28</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>02  03  07  25  33</t>
+          <t>02  04  09  12  36</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000209</v>
+        <v>115000210</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.08.28</t>
+          <t>115.08.29</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>02  04  09  12  36</t>
+          <t>03  06  17  23  33</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000210</v>
+        <v>115000211</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.08.29</t>
+          <t>115.08.31</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>03  06  17  23  33</t>
+          <t>05  10  12  33  39</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000211</v>
+        <v>115000212</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.08.31</t>
+          <t>115.09.01</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>05  10  12  33  39</t>
+          <t>02  04  22  30  38</t>
         </is>
       </c>
     </row>
@@ -1354,16 +1354,16 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.07.30</t>
+          <t>115.08.03</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>08  14  17  19  21  23</t>
+          <t>04  15  22  26  34  36</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
@@ -1374,183 +1374,169 @@
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.08.03</t>
+          <t>115.08.06</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>04  15  22  26  34  36</t>
+          <t>02  07  08  20  26  33</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>04</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.08.06</t>
+          <t>115.08.10</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>02  07  08  20  26  33</t>
+          <t>11  25  28  30  31  36</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.08.10</t>
+          <t>115.08.13</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>11  25  28  30  31  36</t>
+          <t>01  03  04  07  10  19</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.08.13</t>
+          <t>115.08.17</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>01  03  04  07  10  19</t>
+          <t>05  11  18  19  35  38</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>08</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000066</v>
+        <v>115000067</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.08.17</t>
+          <t>115.08.20</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>05  11  18  19  35  38</t>
+          <t>01  02  09  11  29  35</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000067</v>
+        <v>115000068</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.08.20</t>
+          <t>115.08.24</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>01  02  09  11  29  35</t>
+          <t>06  07  09  23  26  36</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000068</v>
+        <v>115000069</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.08.24</t>
+          <t>115.08.27</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>06  07  09  23  26  36</t>
+          <t>02  07  09  11  24  36</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>01</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000069</v>
+        <v>115000070</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.08.27</t>
+          <t>115.08.31</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>02  07  09  11  24  36</t>
+          <t>04  08  12  19  32  37</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
-      <c r="A11" s="4" t="n">
-        <v>115000070</v>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>115.08.31</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>04  08  12  19  32  37</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+      <c r="A11" s="4" t="n"/>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
     </row>
     <row r="12"/>
     <row r="13"/>
@@ -1789,203 +1775,189 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000074</v>
+        <v>115000076</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.07.28</t>
+          <t>115.08.04</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>08  19  24  26  32  43</t>
+          <t>04  09  15  30  36  49</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000075</v>
+        <v>115000077</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.07.31</t>
+          <t>115.08.07</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>11  20  23  33  34  44</t>
+          <t>02  12  19  21  25  41</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>31</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000076</v>
+        <v>115000078</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.08.04</t>
+          <t>115.08.11</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>04  09  15  30  36  49</t>
+          <t>08  12  16  24  29  46</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000077</v>
+        <v>115000079</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.08.07</t>
+          <t>115.08.14</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>02  12  19  21  25  41</t>
+          <t>05  12  25  33  34  35</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000078</v>
+        <v>115000080</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.08.11</t>
+          <t>115.08.18</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>08  12  16  24  29  46</t>
+          <t>01  14  25  27  29  43</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000079</v>
+        <v>115000081</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.08.14</t>
+          <t>115.08.21</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>05  12  25  33  34  35</t>
+          <t>08  14  23  24  26  47</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000080</v>
+        <v>115000082</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.08.18</t>
+          <t>115.08.25</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>01  14  25  27  29  43</t>
+          <t>12  24  26  32  35  40</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000081</v>
+        <v>115000083</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.08.21</t>
+          <t>115.08.28</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>08  14  23  24  26  47</t>
+          <t>09  20  23  26  36  44</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>04</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000082</v>
+        <v>115000084</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.08.25</t>
+          <t>115.09.01</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>12  24  26  32  35  40</t>
+          <t>10  16  19  26  29  48</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
-      <c r="A11" s="4" t="n">
-        <v>115000083</v>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>115.08.28</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>09  20  23  26  36  44</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
-      </c>
+      <c r="A11" s="4" t="n"/>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
     </row>
     <row r="12"/>
     <row r="13"/>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000203</v>
+        <v>115000204</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.08.21</t>
+          <t>115.08.22</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>11  12  18  20  29</t>
+          <t>09  10  29  30  34</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000204</v>
+        <v>115000205</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.08.22</t>
+          <t>115.08.24</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>09  10  29  30  34</t>
+          <t>09  10  19  23  26</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000205</v>
+        <v>115000206</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.08.24</t>
+          <t>115.08.25</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>09  10  19  23  26</t>
+          <t>08  21  23  30  35</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000206</v>
+        <v>115000207</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.08.25</t>
+          <t>115.08.26</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>08  21  23  30  35</t>
+          <t>13  19  23  35  38</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000207</v>
+        <v>115000208</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.08.26</t>
+          <t>115.08.27</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>13  19  23  35  38</t>
+          <t>02  03  07  25  33</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000208</v>
+        <v>115000209</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.08.27</t>
+          <t>115.08.28</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>02  03  07  25  33</t>
+          <t>02  04  09  12  36</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000209</v>
+        <v>115000210</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.08.28</t>
+          <t>115.08.29</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>02  04  09  12  36</t>
+          <t>03  06  17  23  33</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000210</v>
+        <v>115000211</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.08.29</t>
+          <t>115.08.31</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>03  06  17  23  33</t>
+          <t>05  10  12  33  39</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000211</v>
+        <v>115000212</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.08.31</t>
+          <t>115.09.01</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>05  10  12  33  39</t>
+          <t>02  04  22  30  38</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000212</v>
+        <v>115000213</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.09.01</t>
+          <t>115.09.02</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>02  04  22  30  38</t>
+          <t>07  08  13  16  18</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000204</v>
+        <v>115000205</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.08.22</t>
+          <t>115.08.24</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>09  10  29  30  34</t>
+          <t>09  10  19  23  26</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000205</v>
+        <v>115000206</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.08.24</t>
+          <t>115.08.25</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>09  10  19  23  26</t>
+          <t>08  21  23  30  35</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000206</v>
+        <v>115000207</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.08.25</t>
+          <t>115.08.26</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>08  21  23  30  35</t>
+          <t>13  19  23  35  38</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000207</v>
+        <v>115000208</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.08.26</t>
+          <t>115.08.27</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>13  19  23  35  38</t>
+          <t>02  03  07  25  33</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000208</v>
+        <v>115000209</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.08.27</t>
+          <t>115.08.28</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>02  03  07  25  33</t>
+          <t>02  04  09  12  36</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000209</v>
+        <v>115000210</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.08.28</t>
+          <t>115.08.29</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>02  04  09  12  36</t>
+          <t>03  06  17  23  33</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000210</v>
+        <v>115000211</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.08.29</t>
+          <t>115.08.31</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>03  06  17  23  33</t>
+          <t>05  10  12  33  39</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000211</v>
+        <v>115000212</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.08.31</t>
+          <t>115.09.01</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>05  10  12  33  39</t>
+          <t>02  04  22  30  38</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000212</v>
+        <v>115000213</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.09.01</t>
+          <t>115.09.02</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>02  04  22  30  38</t>
+          <t>07  08  13  16  18</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000213</v>
+        <v>115000214</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.09.02</t>
+          <t>115.09.03</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>07  08  13  16  18</t>
+          <t>18  19  22  23  34</t>
         </is>
       </c>
     </row>
@@ -1533,10 +1533,24 @@
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
-      <c r="A11" s="4" t="n"/>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
+      <c r="A11" s="4" t="n">
+        <v>115000071</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>115.09.03</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>01  06  07  19  30  33</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
     </row>
     <row r="12"/>
     <row r="13"/>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000205</v>
+        <v>115000206</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.08.24</t>
+          <t>115.08.25</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>09  10  19  23  26</t>
+          <t>08  21  23  30  35</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000206</v>
+        <v>115000207</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.08.25</t>
+          <t>115.08.26</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>08  21  23  30  35</t>
+          <t>13  19  23  35  38</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000207</v>
+        <v>115000208</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.08.26</t>
+          <t>115.08.27</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>13  19  23  35  38</t>
+          <t>02  03  07  25  33</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000208</v>
+        <v>115000209</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.08.27</t>
+          <t>115.08.28</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>02  03  07  25  33</t>
+          <t>02  04  09  12  36</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000209</v>
+        <v>115000210</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.08.28</t>
+          <t>115.08.29</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>02  04  09  12  36</t>
+          <t>03  06  17  23  33</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000210</v>
+        <v>115000211</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.08.29</t>
+          <t>115.08.31</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>03  06  17  23  33</t>
+          <t>05  10  12  33  39</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000211</v>
+        <v>115000212</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.08.31</t>
+          <t>115.09.01</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>05  10  12  33  39</t>
+          <t>02  04  22  30  38</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000212</v>
+        <v>115000213</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.09.01</t>
+          <t>115.09.02</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>02  04  22  30  38</t>
+          <t>07  08  13  16  18</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000213</v>
+        <v>115000214</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.09.02</t>
+          <t>115.09.03</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>07  08  13  16  18</t>
+          <t>18  19  22  23  34</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000214</v>
+        <v>115000215</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.09.03</t>
+          <t>115.09.04</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>18  19  22  23  34</t>
+          <t>02  04  15  17  24</t>
         </is>
       </c>
     </row>
@@ -1968,10 +1968,24 @@
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
-      <c r="A11" s="4" t="n"/>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
+      <c r="A11" s="4" t="n">
+        <v>115000085</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>115.09.04</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>03  13  17  18  27  37</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
     </row>
     <row r="12"/>
     <row r="13"/>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000206</v>
+        <v>115000207</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.08.25</t>
+          <t>115.08.26</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>08  21  23  30  35</t>
+          <t>13  19  23  35  38</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000207</v>
+        <v>115000208</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.08.26</t>
+          <t>115.08.27</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>13  19  23  35  38</t>
+          <t>02  03  07  25  33</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000208</v>
+        <v>115000209</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.08.27</t>
+          <t>115.08.28</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>02  03  07  25  33</t>
+          <t>02  04  09  12  36</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000209</v>
+        <v>115000210</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.08.28</t>
+          <t>115.08.29</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>02  04  09  12  36</t>
+          <t>03  06  17  23  33</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000210</v>
+        <v>115000211</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.08.29</t>
+          <t>115.08.31</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>03  06  17  23  33</t>
+          <t>05  10  12  33  39</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000211</v>
+        <v>115000212</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.08.31</t>
+          <t>115.09.01</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>05  10  12  33  39</t>
+          <t>02  04  22  30  38</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000212</v>
+        <v>115000213</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.09.01</t>
+          <t>115.09.02</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>02  04  22  30  38</t>
+          <t>07  08  13  16  18</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000213</v>
+        <v>115000214</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.09.02</t>
+          <t>115.09.03</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>07  08  13  16  18</t>
+          <t>18  19  22  23  34</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000214</v>
+        <v>115000215</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.09.03</t>
+          <t>115.09.04</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>18  19  22  23  34</t>
+          <t>02  04  15  17  24</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000215</v>
+        <v>115000216</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.09.04</t>
+          <t>115.09.05</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>02  04  15  17  24</t>
+          <t>03  08  10  28  38</t>
         </is>
       </c>
     </row>
